--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="Q3" t="n">
         <v>1.43</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.83</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>3.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>6.4</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,66 +1907,66 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1975,123 +1975,123 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,66 +2101,66 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,123 +2169,123 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>280</v>
+        <v>85</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>200</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR9" t="n">
         <v>27</v>
       </c>
       <c r="AS9" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC9" t="n">
         <v>17</v>
       </c>
-      <c r="BB9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>16</v>
-      </c>
       <c r="BD9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE9" t="n">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>English Sky Bet Championship</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,61 +2300,61 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>18</v>
       </c>
-      <c r="Y10" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="BA10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>10</v>
       </c>
-      <c r="AH10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>60</v>
-      </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>38</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,66 +2489,66 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I11" t="n">
         <v>4.9</v>
       </c>
-      <c r="I11" t="n">
-        <v>5.7</v>
-      </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>2.32</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2557,123 +2557,123 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,589 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 02:11:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Maringa</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Guarani</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-05-09 02:11:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Inter Limeira</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Santa Cruz PE</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-05-09 02:11:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Paraguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Cerro Porteno</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Guarani (Par)</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-05-09 02:11:24</t>
+          <t>2026-05-09 04:44:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -763,16 +763,16 @@
         <v>2.72</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I2" t="n">
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
         <v>1.81</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>5.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="n">
         <v>1.88</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.96</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.83</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
         <v>2.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
         <v>6.4</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -1930,13 +1930,13 @@
         <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K8" t="n">
         <v>4.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
@@ -2041,7 +2041,7 @@
         <v>14</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
         <v>9</v>
@@ -2050,7 +2050,7 @@
         <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
@@ -2062,7 +2062,7 @@
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BB8" t="n">
         <v>13</v>
@@ -2080,11 +2080,11 @@
         <v>8.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
         <v>4.2</v>
@@ -2160,7 +2160,7 @@
         <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>42</v>
@@ -2196,7 +2196,7 @@
         <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH9" t="n">
         <v>18.5</v>
@@ -2205,13 +2205,13 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
         <v>80</v>
@@ -2226,7 +2226,7 @@
         <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
         <v>27</v>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB9" t="n">
         <v>20</v>
@@ -2265,20 +2265,20 @@
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H10" t="n">
         <v>5.3</v>
@@ -2333,7 +2333,7 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.37</v>
@@ -2342,7 +2342,7 @@
         <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
@@ -2351,10 +2351,10 @@
         <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U10" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2366,10 +2366,10 @@
         <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2378,7 +2378,7 @@
         <v>8.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
         <v>32</v>
@@ -2393,7 +2393,7 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
         <v>95</v>
@@ -2402,16 +2402,16 @@
         <v>19.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="n">
         <v>160</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO10" t="n">
         <v>120</v>
@@ -2426,53 +2426,53 @@
         <v>24</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
         <v>13</v>
       </c>
       <c r="BC10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="BE10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 04:44:48</t>
+          <t>2026-05-09 07:18:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,16 +775,16 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
         <v>1.95</v>
@@ -793,134 +793,134 @@
         <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -969,16 +969,16 @@
         <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P3" t="n">
         <v>2.66</v>
@@ -987,134 +987,134 @@
         <v>1.43</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
@@ -1178,7 +1178,7 @@
         <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
         <v>2.4</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1733,16 @@
         <v>2.76</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.95</v>
       </c>
       <c r="G9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H9" t="n">
         <v>4.1</v>
@@ -2127,10 +2127,10 @@
         <v>4.2</v>
       </c>
       <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR9" t="n">
         <v>27</v>
@@ -2238,7 +2238,7 @@
         <v>9.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV9" t="n">
         <v>15</v>
@@ -2268,17 +2268,17 @@
         <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
         <v>1.82</v>
@@ -2318,7 +2318,7 @@
         <v>5.3</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
         <v>3.8</v>
@@ -2336,25 +2336,25 @@
         <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
         <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T10" t="n">
         <v>1.99</v>
       </c>
       <c r="U10" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
         <v>95</v>
@@ -2381,25 +2381,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI10" t="n">
         <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AK10" t="n">
         <v>26</v>
@@ -2432,7 +2432,7 @@
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2441,10 +2441,10 @@
         <v>10</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>19</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,201 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 07:18:11</t>
+          <t>2026-05-09 09:51:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Guarani (Par)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:51:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,19 +760,19 @@
         <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="H2" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="I2" t="n">
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -808,7 +808,7 @@
         <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
@@ -975,28 +975,28 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P3" t="n">
         <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
         <v>2.12</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
         <v>1.91</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>6.8</v>
+        <v>110</v>
       </c>
       <c r="J4" t="n">
         <v>3.7</v>
@@ -1163,16 +1163,16 @@
         <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
         <v>1.96</v>
@@ -1181,134 +1181,134 @@
         <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,31 +1718,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G7" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,66 +1907,66 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.58</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>2.78</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1975,123 +1975,123 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,66 +2101,66 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G9" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,123 +2169,123 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,66 +2295,66 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Alianza Atletico</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,66 +2489,66 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.32</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2557,123 +2557,123 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,66 +2683,66 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2751,310 +2751,2250 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:33</t>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tondela</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Moreirense</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Guimaraes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rio Ave</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Arouca</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CD Nacional Funchal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Club Football Estrela</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Famalicao</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Inter Limeira</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Santa Cruz PE</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Guarani (Par)</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-05-09 09:51:33</t>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
         <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H3" t="n">
         <v>1.72</v>
@@ -966,7 +966,7 @@
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,7 +975,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.14</v>
@@ -987,112 +987,112 @@
         <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
         <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
         <v>1.03</v>
@@ -1107,14 +1107,14 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
         <v>1.91</v>
@@ -1154,46 +1154,46 @@
         <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>110</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.96</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
         <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
         <v>2.08</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
@@ -1357,16 +1357,16 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
         <v>1.8</v>
@@ -1375,141 +1375,141 @@
         <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.94</v>
+        <v>8.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="H11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU11" t="n">
         <v>6.6</v>
       </c>
-      <c r="I11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN11" t="n">
+      <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX11" t="n">
         <v>9.4</v>
       </c>
-      <c r="AO11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>22</v>
-      </c>
       <c r="BA11" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE11" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,66 +2683,66 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="G12" t="n">
-        <v>1.96</v>
+        <v>1.31</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2751,123 +2751,123 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.02</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>1.93</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>120</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>9</v>
       </c>
-      <c r="AC13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12</v>
-      </c>
       <c r="AR13" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>3.95</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Alianza Atletico</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11.5</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>15.5</v>
+        <v>1.6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.27</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB15" t="n">
         <v>7.6</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,184 +3459,184 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="G16" t="n">
-        <v>1.45</v>
+        <v>1.94</v>
       </c>
       <c r="H16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW16" t="n">
         <v>25</v>
       </c>
-      <c r="Y16" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AX16" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV16" t="n">
+      <c r="AY16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG16" t="n">
         <v>25</v>
       </c>
-      <c r="AW16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="G17" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.28</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W17" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="X17" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>70</v>
       </c>
       <c r="AF17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>12</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AR17" t="n">
         <v>22</v>
       </c>
-      <c r="AI17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN17" t="n">
+      <c r="AS17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF17" t="n">
         <v>12</v>
       </c>
-      <c r="AO17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG17" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Guimaraes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="G18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W18" t="n">
         <v>2.34</v>
       </c>
-      <c r="H18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.74</v>
-      </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AA18" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
         <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Club Football Estrela</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.85</v>
+        <v>11.5</v>
       </c>
       <c r="G19" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="H19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.04</v>
       </c>
-      <c r="I19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="T19" t="n">
         <v>1.87</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.74</v>
-      </c>
       <c r="U19" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>18.5</v>
+        <v>48</v>
       </c>
       <c r="Y19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z19" t="n">
         <v>12</v>
       </c>
-      <c r="Z19" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AA19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI19" t="n">
         <v>32</v>
       </c>
-      <c r="AB19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AJ19" t="n">
+        <v>470</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV19" t="n">
         <v>10</v>
       </c>
-      <c r="AD19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AW19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>19</v>
       </c>
-      <c r="AH19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>15</v>
-      </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>2.88</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>1.79</v>
       </c>
       <c r="H21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.05</v>
       </c>
-      <c r="I21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="K21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,378 +4623,1154 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>CD Nacional Funchal</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N22" t="n">
         <v>3.25</v>
       </c>
-      <c r="I22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-09 12:24:51</t>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Club Football Estrela</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Famalicao</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:58:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>17:45:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:58:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Inter Limeira</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Santa Cruz PE</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:58:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:58:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Guarani (Par)</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:24:51</t>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:58:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -1145,118 +1145,118 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
         <v>1.03</v>
@@ -1265,34 +1265,34 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1301,14 +1301,14 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -1372,13 +1372,13 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>3.2</v>
@@ -1659,16 +1659,16 @@
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.62</v>
+        <v>8.6</v>
       </c>
       <c r="AW6" t="n">
         <v>2.68</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AZ6" t="n">
         <v>4.9</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -1760,10 +1760,10 @@
         <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
         <v>2.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -1939,7 +1939,7 @@
         <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -1951,10 +1951,10 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
         <v>1.46</v>
@@ -1972,7 +1972,7 @@
         <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
@@ -2044,7 +2044,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2065,7 +2065,7 @@
         <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BC8" t="n">
         <v>17.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H9" t="n">
         <v>3.1</v>
@@ -2133,10 +2133,10 @@
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
         <v>4.6</v>
@@ -2151,134 +2151,134 @@
         <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
         <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR9" t="n">
         <v>20</v>
       </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AS9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC9" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="BD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>10</v>
       </c>
-      <c r="AW9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.59</v>
-      </c>
       <c r="BG9" t="n">
-        <v>1.59</v>
+        <v>18.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
         <v>2.8</v>
@@ -2345,7 +2345,7 @@
         <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
         <v>2.22</v>
@@ -2360,7 +2360,7 @@
         <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
@@ -2518,16 +2518,16 @@
         <v>2.62</v>
       </c>
       <c r="K11" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
         <v>1.29</v>
@@ -2536,13 +2536,13 @@
         <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="G12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF12" t="n">
         <v>12.5</v>
       </c>
-      <c r="I12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="AG12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP12" t="n">
         <v>7.2</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Alianza Atletico</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.4</v>
+        <v>1.29</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="H13" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.93</v>
+        <v>7.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>110</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>1.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>4.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6</v>
+        <v>1.78</v>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>1.93</v>
       </c>
       <c r="J15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
         <v>4.3</v>
       </c>
-      <c r="K15" t="n">
+      <c r="O15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB15" t="n">
         <v>4.6</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>13</v>
-      </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>26</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.94</v>
+        <v>4.7</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>1.95</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>2.28</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.27</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
       <c r="X16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02</v>
+        <v>4.1</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>2.28</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>2.86</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
         <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="T17" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="W17" t="n">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.73</v>
+        <v>2.36</v>
       </c>
       <c r="G18" t="n">
-        <v>1.74</v>
+        <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>2.94</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>2.58</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>2.34</v>
+        <v>1.46</v>
       </c>
       <c r="X18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11.5</v>
+        <v>1.63</v>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P19" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="Y19" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV19" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AW19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC19" t="n">
         <v>12</v>
       </c>
-      <c r="AA19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>470</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD19" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.88</v>
+        <v>36</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>1.45</v>
+        <v>2.44</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="I20" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>3.2</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK20" t="n">
         <v>25</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AL20" t="n">
         <v>34</v>
       </c>
-      <c r="Z20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AM20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>20</v>
-      </c>
       <c r="BA20" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="G21" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="T21" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="X21" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA21" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG21" t="n">
         <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AJ21" t="n">
         <v>22</v>
       </c>
       <c r="AK21" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AN21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP21" t="n">
         <v>12</v>
       </c>
-      <c r="AO21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>14</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="AS21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
         <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.3</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF21" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1.74</v>
+        <v>2.66</v>
       </c>
       <c r="X22" t="n">
         <v>14</v>
       </c>
       <c r="Y22" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AK22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>18</v>
       </c>
-      <c r="AE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="AR22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC22" t="n">
         <v>16</v>
       </c>
-      <c r="AG22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN22" t="n">
+      <c r="BD22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE22" t="n">
         <v>25</v>
       </c>
-      <c r="AO22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF22" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Club Football Estrela</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.85</v>
+        <v>1.93</v>
       </c>
       <c r="G23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H23" t="n">
         <v>4.1</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.04</v>
       </c>
-      <c r="I23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X23" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK23" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y23" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AL23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT23" t="n">
         <v>10</v>
       </c>
-      <c r="AD23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="AU23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD23" t="n">
         <v>27</v>
       </c>
-      <c r="AF23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE23" t="n">
-        <v>4.2</v>
+        <v>70</v>
       </c>
       <c r="BF23" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>English Sky Bet Championship</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="H25" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
         <v>3.6</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,378 +5399,2124 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Guimaraes</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="G26" t="n">
-        <v>2.72</v>
+        <v>1.76</v>
       </c>
       <c r="H26" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J26" t="n">
-        <v>2.32</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.52</v>
+        <v>1.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-09 14:58:07</t>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tondela</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Moreirense</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Rio Ave</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N28" t="n">
+        <v>7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X28" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>470</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H29" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Arouca</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CD Nacional Funchal</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X31" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Club Football Estrela</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Famalicao</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>17:45:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Inter Limeira</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Santa Cruz PE</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Guarani (Par)</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q36" t="n">
         <v>1.01</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-05-09 14:58:07</t>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:31:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH36"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,19 +760,19 @@
         <v>2.4</v>
       </c>
       <c r="G2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H2" t="n">
         <v>2.84</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.8</v>
-      </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -793,7 +793,7 @@
         <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -978,10 +978,10 @@
         <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q3" t="n">
         <v>1.5</v>
@@ -1035,10 +1035,10 @@
         <v>23</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
         <v>110</v>
@@ -1056,7 +1056,7 @@
         <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1175,7 +1175,7 @@
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
         <v>1.86</v>
@@ -1247,7 +1247,7 @@
         <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:10:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SFC Opava</t>
+          <t>Al Nasr (UAE)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Al-Ittihad Kalba</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.98</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,22 +1363,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.84</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,103 +1524,103 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>SFC Opava</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8.4</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>9.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.45</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7</v>
+        <v>2.98</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M6" t="n">
         <v>1.01</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
         <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
@@ -1638,72 +1638,72 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.68</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.84</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.84</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,108 +1713,108 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.94</v>
+        <v>8.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.24</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.19</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1832,72 +1832,72 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>2.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="I9" t="n">
         <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,153 +2139,153 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
         <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
         <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>36</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>32</v>
       </c>
       <c r="AK9" t="n">
         <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS9" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AT9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX9" t="n">
         <v>13</v>
       </c>
-      <c r="AR9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>12</v>
       </c>
-      <c r="AW9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13</v>
-      </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG9" t="n">
         <v>18.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.24</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>3.55</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="S10" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.93</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
         <v>3.5</v>
@@ -2515,7 +2515,7 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
         <v>110</v>
@@ -2536,13 +2536,13 @@
         <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2554,7 +2554,7 @@
         <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.29</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="R12" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.98</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>1.72</v>
       </c>
       <c r="X12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI12" t="n">
         <v>46</v>
       </c>
-      <c r="Y12" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>380</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AJ12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX12" t="n">
         <v>14</v>
       </c>
-      <c r="AC12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>10</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,60 +2877,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.29</v>
+        <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>7.2</v>
+        <v>3.55</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>110</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.59</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.26</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,73 +3076,73 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Alianza Atletico</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>1.31</v>
+        <v>1.95</v>
       </c>
       <c r="H14" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.5</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W14" t="n">
         <v>2.04</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="X14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,37 +3151,37 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3193,69 +3193,69 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.93</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.12</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.89</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.78</v>
+        <v>12.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.93</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W15" t="n">
         <v>4.3</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="AA15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,184 +3459,184 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="H17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I17" t="n">
         <v>2.28</v>
       </c>
-      <c r="I17" t="n">
-        <v>2.86</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,34 +3691,34 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U17" t="n">
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,28 +3885,28 @@
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
         <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V18" t="n">
         <v>1.51</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -4046,127 +4046,127 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9</v>
+        <v>2.32</v>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
         <v>1.03</v>
@@ -4175,50 +4175,50 @@
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
         <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
         <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H20" t="n">
         <v>2.9</v>
@@ -4300,7 +4300,7 @@
         <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X20" t="n">
         <v>28</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.14</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.86</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="Y21" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="Z21" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA21" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG21" t="n">
         <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO21" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AP21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC21" t="n">
         <v>12</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ21" t="n">
+      <c r="BD21" t="n">
         <v>20</v>
       </c>
-      <c r="BA21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD21" t="n">
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG21" t="n">
         <v>36</v>
       </c>
-      <c r="BE21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O22" t="n">
         <v>1.39</v>
       </c>
-      <c r="M22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.34</v>
-      </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="AB22" t="n">
         <v>7.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>160</v>
       </c>
       <c r="AN22" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AP22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>18</v>
-      </c>
       <c r="AR22" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AS22" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX22" t="n">
         <v>9</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>8</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD22" t="n">
         <v>36</v>
       </c>
       <c r="BE22" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.36</v>
       </c>
-      <c r="M23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.46</v>
-      </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="X23" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AA23" t="n">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AC23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF23" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AG23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC23" t="n">
         <v>16</v>
       </c>
-      <c r="AE23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BD23" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="G24" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA24" t="n">
         <v>85</v>
       </c>
-      <c r="AA24" t="n">
-        <v>170</v>
-      </c>
       <c r="AB24" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC24" t="n">
         <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AJ24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AM24" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="AP24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>9</v>
-      </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BB24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BC24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BF24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG24" t="n">
         <v>38</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Sky Bet Championship</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="G25" t="n">
-        <v>2.52</v>
+        <v>1.81</v>
       </c>
       <c r="H25" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="T25" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="X25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Z25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
         <v>22</v>
       </c>
-      <c r="AA25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AI25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU25" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE25" t="n">
+      <c r="AV25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW25" t="n">
         <v>34</v>
       </c>
-      <c r="AF25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="AX25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>15.5</v>
       </c>
       <c r="BA25" t="n">
         <v>36</v>
       </c>
       <c r="BB25" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BD25" t="n">
         <v>34</v>
       </c>
       <c r="BE25" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BF25" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="G26" t="n">
-        <v>1.76</v>
+        <v>2.52</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="I26" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
         <v>4.2</v>
       </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.75</v>
-      </c>
       <c r="O26" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="V26" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="W26" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="X26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF26" t="n">
         <v>16</v>
       </c>
-      <c r="Y26" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AJ26" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AK26" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AL26" t="n">
         <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AQ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AR26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BB26" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="BC26" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BE26" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BF26" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -5598,28 +5598,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Club Football Estrela</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.97</v>
+        <v>3.85</v>
       </c>
       <c r="G27" t="n">
-        <v>2.02</v>
+        <v>4.1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>2.14</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
         <v>3.7</v>
@@ -5628,149 +5628,149 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="W27" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP27" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AQ27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
         <v>12</v>
       </c>
-      <c r="AH27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="AS27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG27" t="n">
         <v>11</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>7</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -5792,157 +5792,157 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>CD Nacional Funchal</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>11.5</v>
+        <v>2.18</v>
       </c>
       <c r="G28" t="n">
-        <v>16</v>
+        <v>2.34</v>
       </c>
       <c r="H28" t="n">
-        <v>1.26</v>
+        <v>3.7</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="P28" t="n">
-        <v>3.05</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="T28" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
       </c>
       <c r="V28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX28" t="n">
         <v>4.4</v>
       </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>470</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT28" t="n">
+      <c r="AY28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>4.8</v>
       </c>
-      <c r="AU28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>19</v>
-      </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="BB28" t="n">
         <v>5.2</v>
@@ -5951,20 +5951,20 @@
         <v>5.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.88</v>
+        <v>5.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -5986,179 +5986,179 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="I29" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="K29" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="O29" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P29" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U29" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V29" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="X29" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Z29" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AA29" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="AB29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF29" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AG29" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL29" t="n">
         <v>36</v>
       </c>
       <c r="AM29" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN29" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AP29" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AT29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY29" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>29</v>
+        <v>5.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -6180,31 +6180,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Guimaraes</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H30" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I30" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6213,146 +6213,146 @@
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U30" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W30" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X30" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA30" t="n">
         <v>140</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF30" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO30" t="n">
         <v>85</v>
       </c>
       <c r="AP30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC30" t="n">
         <v>14</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BD30" t="n">
-        <v>5.3</v>
+        <v>27</v>
       </c>
       <c r="BE30" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.34</v>
+        <v>13</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7</v>
+        <v>1.26</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="S31" t="n">
-        <v>3.95</v>
+        <v>2.04</v>
       </c>
       <c r="T31" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="U31" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>4.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.74</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="Y31" t="n">
         <v>14.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>85</v>
+        <v>13.5</v>
       </c>
       <c r="AB31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>470</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV31" t="n">
         <v>10</v>
       </c>
-      <c r="AC31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH31" t="n">
+      <c r="AW31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA31" t="n">
         <v>21</v>
       </c>
-      <c r="AI31" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU31" t="n">
+      <c r="BB31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC31" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD31" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -6568,28 +6568,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Club Football Estrela</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.85</v>
+        <v>1.97</v>
       </c>
       <c r="G32" t="n">
-        <v>4.1</v>
+        <v>2.02</v>
       </c>
       <c r="H32" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="I32" t="n">
-        <v>2.14</v>
+        <v>4.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
         <v>3.7</v>
@@ -6598,156 +6598,156 @@
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.3</v>
       </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.39</v>
-      </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T32" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="U32" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="V32" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="X32" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z32" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AA32" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AB32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD32" t="n">
         <v>18</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX32" t="n">
         <v>10</v>
       </c>
-      <c r="AD32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO32" t="n">
+      <c r="AY32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC32" t="n">
         <v>18</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="BD32" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF32" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="BG32" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>11</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,184 +6951,184 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P34" t="n">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.52</v>
+        <v>1.32</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
@@ -7150,31 +7150,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.97</v>
+        <v>2.32</v>
       </c>
       <c r="G35" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H35" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J35" t="n">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="K35" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -7322,201 +7322,395 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:16</t>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-05-09 20:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Guarani (Par)</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q37" t="n">
         <v>1.01</v>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="inlineStr">
-        <is>
-          <t>2026-05-09 17:31:16</t>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-05-09 20:04:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -787,13 +787,13 @@
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -960,16 +960,16 @@
         <v>1.72</v>
       </c>
       <c r="I3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
@@ -999,7 +999,7 @@
         <v>2.44</v>
       </c>
       <c r="V3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W3" t="n">
         <v>1.25</v>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
         <v>13.5</v>
@@ -1095,26 +1095,26 @@
         <v>18</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
         <v>5.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1262,7 +1262,7 @@
         <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
@@ -1274,7 +1274,7 @@
         <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
@@ -1286,7 +1286,7 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
@@ -1298,17 +1298,17 @@
         <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -1533,31 +1533,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H6" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>2.98</v>
       </c>
       <c r="K6" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
@@ -1569,134 +1569,134 @@
         <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>1.84</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -1784,25 +1784,25 @@
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>8.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AB7" t="n">
         <v>27</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AF7" t="n">
         <v>90</v>
@@ -1847,7 +1847,7 @@
         <v>3.95</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU7" t="n">
         <v>10</v>
@@ -1856,7 +1856,7 @@
         <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AX7" t="n">
         <v>3.1</v>
@@ -1871,10 +1871,10 @@
         <v>3.05</v>
       </c>
       <c r="BB7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BC7" t="n">
         <v>2.86</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.84</v>
       </c>
       <c r="BD7" t="n">
         <v>2.84</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
         <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
         <v>2.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2157,10 +2157,10 @@
         <v>2.74</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.42</v>
@@ -2238,7 +2238,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
@@ -2259,7 +2259,7 @@
         <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="BC9" t="n">
         <v>17.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>7.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>1.93</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.55</v>
       </c>
-      <c r="K11" t="n">
+      <c r="O11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA11" t="n">
         <v>110</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -3088,167 +3088,167 @@
         <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>2.86</v>
       </c>
       <c r="O14" t="n">
         <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q14" t="n">
         <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -3285,10 +3285,10 @@
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
         <v>6.2</v>
@@ -3300,7 +3300,7 @@
         <v>1.22</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
         <v>5.8</v>
@@ -3309,22 +3309,22 @@
         <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
         <v>1.51</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
         <v>2.26</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V15" t="n">
         <v>1.06</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
         <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,146 +3691,146 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
         <v>1.48</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
         <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
         <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="G18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.15</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.96</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
         <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
         <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
         <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -4046,169 +4046,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="G19" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
         <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="U20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.36</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.68</v>
-      </c>
       <c r="X20" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y20" t="n">
         <v>28</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
         <v>21</v>
       </c>
-      <c r="Z20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AI20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO20" t="n">
         <v>60</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>23</v>
       </c>
       <c r="AP20" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC20" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="G21" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="I21" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.57</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.58</v>
-      </c>
       <c r="S21" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="U21" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="X21" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z21" t="n">
         <v>29</v>
       </c>
-      <c r="Y21" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>55</v>
-      </c>
       <c r="AA21" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="AB21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN21" t="n">
         <v>14</v>
       </c>
-      <c r="AC21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AO21" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BG21" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>1.83</v>
       </c>
       <c r="G22" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H22" t="n">
         <v>4.6</v>
@@ -4676,7 +4676,7 @@
         <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T22" t="n">
         <v>2</v>
@@ -4685,10 +4685,10 @@
         <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X22" t="n">
         <v>13.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -4846,10 +4846,10 @@
         <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -4942,7 +4942,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR23" t="n">
         <v>50</v>
@@ -4969,7 +4969,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>40</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G24" t="n">
         <v>1.95</v>
@@ -5109,7 +5109,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
         <v>50</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
         <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
@@ -5246,10 +5246,10 @@
         <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
         <v>2.08</v>
@@ -5264,7 +5264,7 @@
         <v>1.97</v>
       </c>
       <c r="U25" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V25" t="n">
         <v>1.22</v>
@@ -5285,7 +5285,7 @@
         <v>150</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
@@ -5306,7 +5306,7 @@
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ25" t="n">
         <v>18.5</v>
@@ -5339,7 +5339,7 @@
         <v>42</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU25" t="n">
         <v>7.8</v>
@@ -5351,10 +5351,10 @@
         <v>34</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
         <v>19.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Club Football Estrela</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.85</v>
+        <v>11.5</v>
       </c>
       <c r="G27" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="H27" t="n">
-        <v>2.06</v>
+        <v>1.26</v>
       </c>
       <c r="I27" t="n">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>2.04</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="U27" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.87</v>
+        <v>4.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>18.5</v>
+        <v>46</v>
       </c>
       <c r="Y27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z27" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z27" t="n">
-        <v>16</v>
-      </c>
       <c r="AA27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI27" t="n">
         <v>32</v>
       </c>
-      <c r="AB27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AJ27" t="n">
+        <v>470</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>19</v>
       </c>
-      <c r="AH27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>15</v>
-      </c>
       <c r="BA27" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>44</v>
+        <v>6.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Club Football Estrela</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.18</v>
+        <v>3.85</v>
       </c>
       <c r="G28" t="n">
-        <v>2.34</v>
+        <v>4.1</v>
       </c>
       <c r="H28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.7</v>
       </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.25</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.95</v>
-      </c>
       <c r="T28" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AA28" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AB28" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO28" t="n">
         <v>18</v>
       </c>
-      <c r="AE28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG28" t="n">
+      <c r="AP28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT28" t="n">
         <v>13</v>
       </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ28" t="n">
+      <c r="AU28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW28" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.6</v>
       </c>
       <c r="AX28" t="n">
         <v>4.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB28" t="n">
         <v>4.8</v>
       </c>
-      <c r="BA28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BC28" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.5</v>
+        <v>44</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -5986,179 +5986,179 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>CD Nacional Funchal</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="H29" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="I29" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.95</v>
       </c>
-      <c r="K29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.05</v>
-      </c>
       <c r="T29" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U29" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>2.24</v>
+        <v>1.74</v>
       </c>
       <c r="X29" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AA29" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF29" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
         <v>70</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AK29" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AL29" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AM29" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AO29" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AP29" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ29" t="n">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="AW29" t="n">
         <v>5.9</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="BA29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD29" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG29" t="n">
         <v>6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -6180,179 +6180,179 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="H30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I30" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R30" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T30" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V30" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W30" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="X30" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA30" t="n">
         <v>140</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH30" t="n">
         <v>22</v>
       </c>
-      <c r="AE30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>21</v>
-      </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM30" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>85</v>
       </c>
       <c r="AP30" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB30" t="n">
         <v>15.5</v>
       </c>
-      <c r="AR30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BC30" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>27</v>
+        <v>5.4</v>
       </c>
       <c r="BE30" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BF30" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Guimaraes</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>11.5</v>
+        <v>1.74</v>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>1.76</v>
       </c>
       <c r="H31" t="n">
-        <v>1.26</v>
+        <v>5.1</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="K31" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="R31" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="U31" t="n">
         <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>4.4</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="X31" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="Y31" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN31" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="AO31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC31" t="n">
         <v>14</v>
       </c>
-      <c r="AE31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>470</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="BD31" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE31" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV31" t="n">
+      <c r="BF31" t="n">
         <v>10</v>
       </c>
-      <c r="AW31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG31" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>3.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -6619,7 +6619,7 @@
         <v>3.6</v>
       </c>
       <c r="T32" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="U32" t="n">
         <v>2.02</v>
@@ -6667,7 +6667,7 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK32" t="n">
         <v>23</v>
@@ -6694,10 +6694,10 @@
         <v>28</v>
       </c>
       <c r="AS32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU32" t="n">
         <v>7.2</v>
@@ -6706,7 +6706,7 @@
         <v>15.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX32" t="n">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB32" t="n">
         <v>20</v>
@@ -6730,17 +6730,17 @@
         <v>34</v>
       </c>
       <c r="BE32" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF32" t="n">
         <v>13.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.44</v>
       </c>
       <c r="G33" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H33" t="n">
         <v>7.8</v>
@@ -6789,7 +6789,7 @@
         <v>5.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
         <v>1.04</v>
@@ -6804,7 +6804,7 @@
         <v>2.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R33" t="n">
         <v>1.5</v>
@@ -6816,13 +6816,13 @@
         <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="V33" t="n">
         <v>1.13</v>
       </c>
       <c r="W33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X33" t="n">
         <v>23</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.32</v>
+        <v>2.06</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
         <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
         <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
         <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG34" t="n">
         <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,184 +7145,184 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P35" t="n">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.38</v>
+        <v>1.32</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -7344,179 +7344,179 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="G36" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J36" t="n">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="K36" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P36" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>
@@ -7565,16 +7565,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P37" t="n">
         <v>1.24</v>
@@ -7583,134 +7583,522 @@
         <v>1.01</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-09 20:04:20</t>
+          <t>2026-05-09 22:37:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:37:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:37:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
         <v>2.84</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -778,149 +778,149 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
         <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
         <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>1.72</v>
       </c>
       <c r="I3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
@@ -1160,7 +1160,7 @@
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.34</v>
@@ -1169,7 +1169,7 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
@@ -1190,13 +1190,13 @@
         <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I6" t="n">
         <v>3.7</v>
@@ -1548,7 +1548,7 @@
         <v>2.98</v>
       </c>
       <c r="K6" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.32</v>
@@ -1563,7 +1563,7 @@
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
         <v>1.84</v>
@@ -1575,7 +1575,7 @@
         <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1584,7 +1584,7 @@
         <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
         <v>18.5</v>
@@ -1599,7 +1599,7 @@
         <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
         <v>9.800000000000001</v>
@@ -1632,7 +1632,7 @@
         <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
         <v>25</v>
@@ -1641,62 +1641,62 @@
         <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
         <v>3.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>9.800000000000001</v>
@@ -1751,19 +1751,19 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1772,7 +1772,7 @@
         <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
         <v>3</v>
@@ -1784,7 +1784,7 @@
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>8.4</v>
@@ -1805,13 +1805,13 @@
         <v>970</v>
       </c>
       <c r="AF7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AG7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI7" t="n">
         <v>55</v>
@@ -1820,10 +1820,10 @@
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1835,19 +1835,19 @@
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR7" t="n">
         <v>3.2</v>
       </c>
-      <c r="AR7" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AS7" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AU7" t="n">
         <v>10</v>
@@ -1856,41 +1856,41 @@
         <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="AX7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG7" t="n">
         <v>3.1</v>
       </c>
-      <c r="AY7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -1954,10 +1954,10 @@
         <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
         <v>2.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2157,7 +2157,7 @@
         <v>2.74</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
         <v>2.3</v>
@@ -2223,7 +2223,7 @@
         <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
         <v>11.5</v>
@@ -2238,7 +2238,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
@@ -2259,7 +2259,7 @@
         <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BC9" t="n">
         <v>17.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>7.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -2548,7 +2548,7 @@
         <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
         <v>1.29</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>2.34</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
         <v>2.86</v>
@@ -3118,7 +3118,7 @@
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
         <v>1.23</v>
@@ -3127,25 +3127,25 @@
         <v>3.95</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3154,7 +3154,7 @@
         <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>29</v>
@@ -3169,7 +3169,7 @@
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.45</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AU14" t="n">
         <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AZ14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB14" t="n">
         <v>3.75</v>
       </c>
-      <c r="BA14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BC14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
         <v>1.22</v>
@@ -3330,13 +3330,13 @@
         <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X15" t="n">
         <v>30</v>
       </c>
       <c r="Y15" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
         <v>160</v>
@@ -3354,7 +3354,7 @@
         <v>55</v>
       </c>
       <c r="AE15" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AF15" t="n">
         <v>8.800000000000001</v>
@@ -3363,10 +3363,10 @@
         <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI15" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AJ15" t="n">
         <v>10</v>
@@ -3387,16 +3387,16 @@
         <v>350</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>38</v>
       </c>
       <c r="AR15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS15" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10.5</v>
       </c>
       <c r="AT15" t="n">
         <v>9</v>
@@ -3405,22 +3405,22 @@
         <v>13</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BB15" t="n">
         <v>8.4</v>
@@ -3429,20 +3429,20 @@
         <v>11.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>3.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.15</v>
+        <v>1.63</v>
       </c>
       <c r="G17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J17" t="n">
         <v>4.3</v>
       </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>2.34</v>
       </c>
       <c r="X17" t="n">
         <v>29</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Z17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
         <v>20</v>
       </c>
-      <c r="AA17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>17</v>
+        <v>5.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.96</v>
+        <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>3.45</v>
+        <v>2.46</v>
       </c>
       <c r="H18" t="n">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Y18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG18" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AH18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI18" t="n">
         <v>40</v>
       </c>
-      <c r="AB18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AJ18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN18" t="n">
         <v>14</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>38</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
       </c>
       <c r="AP18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX18" t="n">
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
         <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -4046,163 +4046,163 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="G19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.15</v>
       </c>
-      <c r="H19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.22</v>
-      </c>
       <c r="T19" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE19" t="n">
         <v>32</v>
       </c>
-      <c r="Y19" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="AF19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH19" t="n">
         <v>21</v>
       </c>
-      <c r="AC19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>970</v>
-      </c>
       <c r="AI19" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AO19" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
         <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
         <v>1.01</v>
@@ -4214,11 +4214,11 @@
         <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.64</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H20" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.59</v>
-      </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="T20" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>2.36</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK20" t="n">
         <v>29</v>
       </c>
-      <c r="Y20" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AO20" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AP20" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -4434,34 +4434,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.16</v>
+        <v>3.15</v>
       </c>
       <c r="G21" t="n">
-        <v>2.46</v>
+        <v>4.3</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
@@ -4473,140 +4473,140 @@
         <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.56</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="S21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="W21" t="n">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="X21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN21" t="n">
         <v>29</v>
       </c>
-      <c r="AA21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AO21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AU21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
         <v>17.5</v>
       </c>
-      <c r="AI21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG21" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>1.83</v>
       </c>
       <c r="G22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H22" t="n">
         <v>4.6</v>
@@ -4655,7 +4655,7 @@
         <v>3.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
@@ -4664,13 +4664,13 @@
         <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
         <v>1.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
@@ -4679,7 +4679,7 @@
         <v>3.95</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U22" t="n">
         <v>1.9</v>
@@ -4703,7 +4703,7 @@
         <v>150</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC22" t="n">
         <v>8.800000000000001</v>
@@ -4739,7 +4739,7 @@
         <v>160</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO22" t="n">
         <v>110</v>
@@ -4790,17 +4790,17 @@
         <v>36</v>
       </c>
       <c r="BE22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
         <v>12.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
         <v>8.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH23" t="n">
         <v>25</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.94</v>
       </c>
       <c r="G24" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
         <v>4.1</v>
       </c>
-      <c r="I24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
         <v>4.2</v>
@@ -5073,7 +5073,7 @@
         <v>2.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W24" t="n">
         <v>2.04</v>
@@ -5109,7 +5109,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI24" t="n">
         <v>50</v>
@@ -5133,7 +5133,7 @@
         <v>42</v>
       </c>
       <c r="AP24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ24" t="n">
         <v>16</v>
@@ -5142,7 +5142,7 @@
         <v>29</v>
       </c>
       <c r="AS24" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
         <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
@@ -5300,7 +5300,7 @@
         <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
@@ -5354,7 +5354,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
         <v>19.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
         <v>4.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
         <v>2.06</v>
@@ -5569,14 +5569,14 @@
         <v>34</v>
       </c>
       <c r="BF26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG26" t="n">
         <v>24</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Club Football Estrela</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" t="n">
         <v>11.5</v>
       </c>
-      <c r="G27" t="n">
+      <c r="Z27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT27" t="n">
         <v>13</v>
       </c>
-      <c r="H27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" t="n">
+      <c r="AU27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW27" t="n">
         <v>4.3</v>
       </c>
-      <c r="W27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="AX27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY27" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>470</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>3.3</v>
+        <v>11</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Club Football Estrela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.85</v>
+        <v>1.71</v>
       </c>
       <c r="G28" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.06</v>
+        <v>5.3</v>
       </c>
       <c r="I28" t="n">
-        <v>2.14</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O28" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T28" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="U28" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="V28" t="n">
-        <v>1.87</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.32</v>
+        <v>2.26</v>
       </c>
       <c r="X28" t="n">
         <v>18.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="AA28" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="AB28" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC28" t="n">
         <v>9.6</v>
       </c>
       <c r="AD28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>36</v>
-      </c>
       <c r="AG28" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
         <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="AP28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AS28" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>30</v>
+        <v>5.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.8</v>
+        <v>15.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>44</v>
+        <v>5.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -5986,179 +5986,179 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="G29" t="n">
-        <v>2.34</v>
+        <v>1.46</v>
       </c>
       <c r="H29" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>3.95</v>
+        <v>2.68</v>
       </c>
       <c r="T29" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="W29" t="n">
-        <v>1.74</v>
+        <v>3.15</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y29" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="Z29" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="n">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="AB29" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AE29" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AI29" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AJ29" t="n">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AL29" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AM29" t="n">
         <v>130</v>
       </c>
       <c r="AN29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>25</v>
       </c>
-      <c r="AO29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AR29" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW29" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AX29" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -6180,179 +6180,179 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>CD Nacional Funchal</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="G30" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="H30" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="I30" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" t="n">
         <v>1.33</v>
       </c>
-      <c r="M30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W30" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="X30" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AA30" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
         <v>70</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AK30" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AL30" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AM30" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AO30" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AP30" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="AW30" t="n">
         <v>5.9</v>
       </c>
       <c r="AX30" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="BA30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD30" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG30" t="n">
         <v>6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
         <v>18.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM31" t="n">
         <v>130</v>
@@ -6491,7 +6491,7 @@
         <v>85</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ31" t="n">
         <v>15.5</v>
@@ -6521,7 +6521,7 @@
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA31" t="n">
         <v>10</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>2.02</v>
       </c>
       <c r="H32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I32" t="n">
         <v>4.6</v>
@@ -6619,7 +6619,7 @@
         <v>3.6</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U32" t="n">
         <v>2.02</v>
@@ -6643,7 +6643,7 @@
         <v>110</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC32" t="n">
         <v>8.4</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -6762,179 +6762,179 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.44</v>
+        <v>11.5</v>
       </c>
       <c r="G33" t="n">
+        <v>13</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1.46</v>
       </c>
-      <c r="H33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.64</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="S33" t="n">
-        <v>2.68</v>
+        <v>2.04</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U33" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.13</v>
+        <v>4.5</v>
       </c>
       <c r="W33" t="n">
-        <v>3.15</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Y33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI33" t="n">
         <v>32</v>
       </c>
-      <c r="Z33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AJ33" t="n">
+        <v>470</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS33" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN33" t="n">
+      <c r="AT33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB33" t="n">
         <v>6.6</v>
       </c>
-      <c r="AO33" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC33" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="BD33" t="n">
-        <v>29</v>
+        <v>6.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -6974,16 +6974,16 @@
         <v>4.3</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K34" t="n">
         <v>3.9</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
@@ -6995,7 +6995,7 @@
         <v>1.36</v>
       </c>
       <c r="P34" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q34" t="n">
         <v>2.06</v>
@@ -7031,7 +7031,7 @@
         <v>140</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC34" t="n">
         <v>9.800000000000001</v>
@@ -7073,7 +7073,7 @@
         <v>110</v>
       </c>
       <c r="AP34" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ34" t="n">
         <v>10.5</v>
@@ -7097,7 +7097,7 @@
         <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY34" t="n">
         <v>7.8</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -7344,31 +7344,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="G36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J36" t="n">
         <v>2.8</v>
       </c>
-      <c r="H36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.82</v>
-      </c>
       <c r="K36" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7377,22 +7377,22 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="O36" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="P36" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="R36" t="n">
         <v>1.17</v>
       </c>
       <c r="S36" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -7401,10 +7401,10 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7538,49 +7538,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="O37" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -7589,70 +7589,70 @@
         <v>1.01</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP37" t="n">
         <v>1.03</v>
@@ -7710,14 +7710,14 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,31 +7732,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7765,22 +7765,22 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="O38" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P38" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R38" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-09 22:37:11</t>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>
@@ -7935,170 +7935,752 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="G39" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H39" t="n">
         <v>1.72</v>
       </c>
       <c r="I39" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="J39" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K39" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P39" t="n">
         <v>1.84</v>
       </c>
       <c r="Q39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>95</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-05-10 01:09:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2.08</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="R40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-05-10 01:09:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X41" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-05-10 01:09:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Peruvian Primera Division</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sport Boys (Per)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J42" t="n">
         <v>3.5</v>
       </c>
-      <c r="T39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V39" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X39" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z39" t="n">
+      <c r="K42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z42" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="AA42" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG42" t="n">
         <v>22</v>
       </c>
-      <c r="AC39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ39" t="n">
+      <c r="AH42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA42" t="n">
         <v>5</v>
       </c>
-      <c r="AR39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>2026-05-09 22:37:11</t>
+      <c r="BB42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-05-10 01:09:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH42"/>
+  <dimension ref="A1:BH44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,37 +781,37 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
         <v>15</v>
@@ -820,13 +820,13 @@
         <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>15.5</v>
@@ -835,10 +835,10 @@
         <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>19</v>
@@ -847,22 +847,22 @@
         <v>48</v>
       </c>
       <c r="AJ2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL2" t="n">
         <v>42</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
         <v>1.03</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -990,19 +990,19 @@
         <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
@@ -1017,10 +1017,10 @@
         <v>24</v>
       </c>
       <c r="AB3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
         <v>13</v>
@@ -1029,31 +1029,31 @@
         <v>20</v>
       </c>
       <c r="AF3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
         <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
         <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
         <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO3" t="n">
         <v>8.6</v>
@@ -1062,10 +1062,10 @@
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
         <v>14.5</v>
@@ -1077,7 +1077,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
         <v>12</v>
@@ -1110,11 +1110,11 @@
         <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
         <v>1.86</v>
@@ -1202,7 +1202,7 @@
         <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z4" t="n">
         <v>38</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1581,16 +1581,16 @@
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
         <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>27</v>
@@ -1599,13 +1599,13 @@
         <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
         <v>42</v>
@@ -1614,7 +1614,7 @@
         <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>20</v>
@@ -1641,13 +1641,13 @@
         <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>3.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AS6" t="n">
         <v>4.2</v>
@@ -1665,13 +1665,13 @@
         <v>4</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.82</v>
+        <v>3.65</v>
       </c>
       <c r="AY6" t="n">
         <v>3.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="BA6" t="n">
         <v>4.1</v>
@@ -1692,18 +1692,18 @@
         <v>2.88</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,112 +1718,112 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>FC Spaeri</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.45</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1832,72 +1832,72 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,33 +1907,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.96</v>
+        <v>7.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>1.55</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>4.9</v>
@@ -1942,82 +1942,82 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>2.82</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2026,72 +2026,72 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.24</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.3</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="P9" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>1.33</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>2.92</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>1.98</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>55</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
         <v>14.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.6</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>12</v>
       </c>
-      <c r="AU10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>6</v>
-      </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.96</v>
+        <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>1.33</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="L11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.34</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
         <v>3.55</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AO11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="BA11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB11" t="n">
         <v>10</v>
       </c>
-      <c r="AD11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="BC11" t="n">
         <v>12</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BD11" t="n">
-        <v>3.9</v>
+        <v>19</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="G12" t="n">
-        <v>2.78</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.34</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
         <v>3.1</v>
@@ -2906,7 +2906,7 @@
         <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -2936,13 +2936,13 @@
         <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
         <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X13" t="n">
         <v>24</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.74</v>
+        <v>1.02</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.86</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.95</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>1.29</v>
+        <v>2.54</v>
       </c>
       <c r="H15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X15" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG15" t="n">
         <v>14</v>
       </c>
-      <c r="I15" t="n">
-        <v>18</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>220</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>350</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Alianza Atletico</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.4</v>
+        <v>1.74</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.91</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.75</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.18</v>
-      </c>
       <c r="V16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W16" t="n">
         <v>2.08</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AA16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
         <v>970</v>
       </c>
-      <c r="AF16" t="n">
-        <v>44</v>
-      </c>
       <c r="AG16" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
         <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF16" t="n">
         <v>12</v>
       </c>
-      <c r="AP16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BG16" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="G17" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>5.7</v>
+        <v>17.5</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="R17" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="T17" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>2.34</v>
+        <v>4.4</v>
       </c>
       <c r="X17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y17" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Z17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD17" t="n">
         <v>55</v>
       </c>
-      <c r="AA17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>24</v>
-      </c>
       <c r="AE17" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="AP17" t="n">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV17" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV17" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AW17" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AX17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE17" t="n">
         <v>9.4</v>
       </c>
-      <c r="AY17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF17" t="n">
-        <v>5.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.16</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.42</v>
-      </c>
       <c r="Q18" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="T18" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="X18" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA18" t="n">
         <v>21</v>
       </c>
-      <c r="Z18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>60</v>
-      </c>
       <c r="AB18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AC18" t="n">
         <v>11.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF18" t="n">
         <v>36</v>
       </c>
-      <c r="AF18" t="n">
-        <v>21</v>
-      </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AH18" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AP18" t="n">
-        <v>18.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX18" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -4046,163 +4046,163 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="G19" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>46</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>65</v>
-      </c>
       <c r="AK19" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
         <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
         <v>1.01</v>
@@ -4214,11 +4214,11 @@
         <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -4240,163 +4240,163 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="G20" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="H20" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="I20" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.58</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="R20" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE20" t="n">
         <v>32</v>
       </c>
-      <c r="Y20" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AF20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH20" t="n">
         <v>21</v>
       </c>
-      <c r="AC20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>970</v>
-      </c>
       <c r="AI20" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AO20" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
         <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
         <v>1.01</v>
@@ -4408,11 +4408,11 @@
         <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>4.3</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I21" t="n">
         <v>2.22</v>
@@ -4473,13 +4473,13 @@
         <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q21" t="n">
         <v>1.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
         <v>2.4</v>
@@ -4494,10 +4494,10 @@
         <v>1.81</v>
       </c>
       <c r="W21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y21" t="n">
         <v>17</v>
@@ -4521,7 +4521,7 @@
         <v>24</v>
       </c>
       <c r="AF21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG21" t="n">
         <v>18.5</v>
@@ -4533,7 +4533,7 @@
         <v>34</v>
       </c>
       <c r="AJ21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK21" t="n">
         <v>42</v>
@@ -4599,21 +4599,21 @@
         <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG21" t="n">
         <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="G22" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N22" t="n">
         <v>5.2</v>
       </c>
-      <c r="J22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="S22" t="n">
-        <v>3.95</v>
+        <v>2.42</v>
       </c>
       <c r="T22" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="X22" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="Z22" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AF22" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
         <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AM22" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AO22" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AP22" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ22" t="n">
+      <c r="BA22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD22" t="n">
         <v>20</v>
       </c>
-      <c r="BA22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>36</v>
-      </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF22" t="n">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="H23" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="I23" t="n">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="U23" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="V23" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>2.66</v>
+        <v>1.7</v>
       </c>
       <c r="X23" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG23" t="n">
         <v>14</v>
       </c>
-      <c r="Y23" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AH23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK23" t="n">
         <v>25</v>
       </c>
-      <c r="AI23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AR23" t="n">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
         <v>16</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="G24" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="O24" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="V24" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="X24" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA24" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AB24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AG24" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AJ24" t="n">
         <v>22</v>
       </c>
       <c r="AK24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB24" t="n">
         <v>18.5</v>
       </c>
-      <c r="AL24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>21</v>
-      </c>
       <c r="BC24" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BE24" t="n">
-        <v>70</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF24" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="G25" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="X25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>90</v>
+      </c>
+      <c r="BB25" t="n">
         <v>13</v>
       </c>
-      <c r="Y25" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="BC25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD25" t="n">
         <v>36</v>
       </c>
-      <c r="AS25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>34</v>
-      </c>
       <c r="BE25" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.48</v>
+        <v>1.94</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U26" t="n">
         <v>2.3</v>
       </c>
       <c r="V26" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AA26" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AF26" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH26" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AM26" t="n">
         <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AR26" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AS26" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AX26" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BB26" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BD26" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BE26" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BF26" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>English Sky Bet Championship</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Club Football Estrela</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J27" t="n">
         <v>3.85</v>
       </c>
-      <c r="G27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.55</v>
       </c>
-      <c r="K27" t="n">
+      <c r="O27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.7</v>
       </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T27" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="V27" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>2.24</v>
       </c>
       <c r="X27" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="Y27" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="Z27" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AA27" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="AB27" t="n">
-        <v>18</v>
+        <v>8.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AG27" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AH27" t="n">
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>95</v>
+        <v>18.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO27" t="n">
         <v>110</v>
       </c>
-      <c r="AN27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>18</v>
-      </c>
       <c r="AP27" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AS27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>19.5</v>
       </c>
-      <c r="AT27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY27" t="n">
+      <c r="BA27" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF27" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG27" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,184 +5787,184 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="H28" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
         <v>1.28</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
         <v>1.72</v>
       </c>
       <c r="U28" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>2.26</v>
+        <v>1.64</v>
       </c>
       <c r="X28" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AF28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG28" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AN28" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="AP28" t="n">
         <v>14</v>
       </c>
       <c r="AQ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF28" t="n">
         <v>16</v>
       </c>
-      <c r="AR28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -5986,179 +5986,179 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Football Estrela</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.44</v>
+        <v>3.85</v>
       </c>
       <c r="G29" t="n">
-        <v>1.46</v>
+        <v>4.1</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="I29" t="n">
-        <v>8.199999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="J29" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="P29" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="V29" t="n">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="W29" t="n">
-        <v>3.15</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA29" t="n">
         <v>32</v>
       </c>
-      <c r="Z29" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>280</v>
-      </c>
       <c r="AB29" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AC29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD29" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD29" t="n">
-        <v>32</v>
-      </c>
       <c r="AE29" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AG29" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
         <v>110</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AN29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AK29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AQ29" t="n">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>26</v>
+        <v>9.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BB29" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BE29" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -6192,19 +6192,19 @@
         <v>2.18</v>
       </c>
       <c r="G30" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H30" t="n">
         <v>3.7</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6222,7 +6222,7 @@
         <v>1.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R30" t="n">
         <v>1.29</v>
@@ -6231,13 +6231,13 @@
         <v>3.95</v>
       </c>
       <c r="T30" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
         <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
         <v>1.75</v>
@@ -6255,7 +6255,7 @@
         <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC30" t="n">
         <v>7.8</v>
@@ -6300,13 +6300,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS30" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT30" t="n">
         <v>7.8</v>
@@ -6315,44 +6315,44 @@
         <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BA30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE30" t="n">
         <v>6</v>
       </c>
-      <c r="BB30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BG30" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="G31" t="n">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="H31" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="I31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K31" t="n">
         <v>5.4</v>
       </c>
-      <c r="J31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="P31" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="T31" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="W31" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="X31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK31" t="n">
         <v>16</v>
       </c>
-      <c r="Y31" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM31" t="n">
         <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="AO31" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS31" t="n">
         <v>10.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AW31" t="n">
         <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>10</v>
       </c>
       <c r="BB31" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE31" t="n">
         <v>10.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -6568,179 +6568,179 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="G32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.02</v>
       </c>
-      <c r="H32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.83</v>
-      </c>
       <c r="Q32" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="T32" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="U32" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V32" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="X32" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Z32" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AA32" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB32" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE32" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF32" t="n">
         <v>12.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI32" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK32" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AL32" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AM32" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV32" t="n">
         <v>17</v>
       </c>
-      <c r="AO32" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB32" t="n">
         <v>15.5</v>
       </c>
-      <c r="AW32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>20</v>
-      </c>
       <c r="BC32" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BF32" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -6762,186 +6762,186 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Guimaraes</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>11.5</v>
+        <v>1.74</v>
       </c>
       <c r="G33" t="n">
-        <v>13</v>
+        <v>1.76</v>
       </c>
       <c r="H33" t="n">
-        <v>1.26</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="U33" t="n">
         <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>4.5</v>
+        <v>1.22</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="X33" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="Y33" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN33" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AO33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC33" t="n">
         <v>14</v>
       </c>
-      <c r="AE33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>470</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ33" t="n">
+      <c r="BD33" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE33" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV33" t="n">
+      <c r="BF33" t="n">
         <v>10</v>
       </c>
-      <c r="AW33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG33" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="G34" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H34" t="n">
         <v>4.3</v>
       </c>
       <c r="I34" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P34" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q34" t="n">
         <v>2.06</v>
       </c>
       <c r="R34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.28</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X34" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y34" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AA34" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>23</v>
       </c>
-      <c r="AE34" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ34" t="n">
+      <c r="AK34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR34" t="n">
         <v>28</v>
       </c>
-      <c r="AK34" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN34" t="n">
+      <c r="AS34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB34" t="n">
         <v>20</v>
       </c>
-      <c r="AO34" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ34" t="n">
+      <c r="BC34" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE34" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF34" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>6.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.82</v>
       </c>
       <c r="S35" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="G36" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="H36" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J36" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="K36" t="n">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P36" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>2.06</v>
+        <v>3.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V36" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W36" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV36" t="n">
         <v>1.03</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ36" t="n">
         <v>1.03</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
         <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG36" t="n">
         <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,174 +7533,174 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="O37" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="P37" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.44</v>
+        <v>1.32</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="T37" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
         <v>1.01</v>
@@ -7710,14 +7710,14 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,31 +7732,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7765,22 +7765,22 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="O38" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S38" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,191 +7921,191 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5.1</v>
+        <v>2.28</v>
       </c>
       <c r="G39" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="H39" t="n">
-        <v>1.72</v>
+        <v>3.1</v>
       </c>
       <c r="I39" t="n">
-        <v>1.88</v>
+        <v>4.3</v>
       </c>
       <c r="J39" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP39" t="n">
         <v>3.4</v>
       </c>
-      <c r="K39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>95</v>
+        <v>4.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8115,36 +8115,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8153,22 +8153,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="O40" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P40" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R40" t="n">
         <v>1.18</v>
       </c>
       <c r="S40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -8177,10 +8177,10 @@
         <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8237,52 +8237,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8309,378 +8309,766 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
       <c r="G41" t="n">
-        <v>2.94</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>2.56</v>
+        <v>1.72</v>
       </c>
       <c r="I41" t="n">
-        <v>3.15</v>
+        <v>1.87</v>
       </c>
       <c r="J41" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K41" t="n">
         <v>4.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P41" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S41" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="T41" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U41" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="V41" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="W41" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="X41" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
         <v>15</v>
       </c>
-      <c r="Y41" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>48</v>
-      </c>
       <c r="AP41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX41" t="n">
         <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-05-10 03:41:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X43" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-05-10 03:41:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Peruvian Primera Division</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Sport Boys (Per)</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Universitario de Deportes</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K44" t="n">
         <v>4.1</v>
       </c>
-      <c r="G42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K42" t="n">
+      <c r="L44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT44" t="n">
         <v>4.2</v>
       </c>
-      <c r="L42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X42" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS42" t="n">
+      <c r="AU44" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW44" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW42" t="n">
+      <c r="AX44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ44" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY42" t="n">
+      <c r="BA44" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG44" t="n">
         <v>4.5</v>
       </c>
-      <c r="AZ42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH42" t="inlineStr">
-        <is>
-          <t>2026-05-10 01:09:37</t>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -763,7 +763,7 @@
         <v>2.5</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
         <v>3.55</v>
@@ -808,7 +808,7 @@
         <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -951,28 +951,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
         <v>5.6</v>
@@ -999,10 +999,10 @@
         <v>2.46</v>
       </c>
       <c r="V3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="H4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.3</v>
       </c>
-      <c r="I4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
         <v>1.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
@@ -1214,31 +1214,31 @@
         <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
@@ -1247,10 +1247,10 @@
         <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
@@ -1268,7 +1268,7 @@
         <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
         <v>14</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1360,22 +1360,22 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
         <v>1.17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
         <v>1.17</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>4.5</v>
@@ -1563,7 +1563,7 @@
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
         <v>1.84</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1748,16 +1748,16 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q7" t="n">
         <v>1.35</v>
@@ -1766,7 +1766,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G8" t="n">
         <v>10.5</v>
@@ -1930,7 +1930,7 @@
         <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
@@ -1963,13 +1963,13 @@
         <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="W8" t="n">
         <v>1.11</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.96</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
@@ -2136,7 +2136,7 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
         <v>2.24</v>
@@ -2148,10 +2148,10 @@
         <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
         <v>2.5</v>
@@ -2166,7 +2166,7 @@
         <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2324,10 +2324,10 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2336,28 +2336,28 @@
         <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q10" t="n">
         <v>1.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
         <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
         <v>1.67</v>
@@ -2375,7 +2375,7 @@
         <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC10" t="n">
         <v>10.5</v>
@@ -2402,7 +2402,7 @@
         <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
         <v>38</v>
@@ -2411,10 +2411,10 @@
         <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
@@ -2515,19 +2515,19 @@
         <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K11" t="n">
         <v>7.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.13</v>
@@ -2536,31 +2536,31 @@
         <v>3.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="R11" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
         <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X11" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="Y11" t="n">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="Z11" t="n">
         <v>130</v>
@@ -2569,31 +2569,31 @@
         <v>380</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD11" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AE11" t="n">
         <v>160</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK11" t="n">
         <v>13.5</v>
@@ -2617,22 +2617,22 @@
         <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV11" t="n">
         <v>23</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
         <v>9.6</v>
@@ -2644,7 +2644,7 @@
         <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
@@ -2656,17 +2656,17 @@
         <v>19</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2697,76 +2697,76 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G12" t="n">
         <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I12" t="n">
         <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.79</v>
-      </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
         <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>21</v>
@@ -2775,7 +2775,7 @@
         <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
         <v>13</v>
@@ -2802,22 +2802,22 @@
         <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.05</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
@@ -2826,7 +2826,7 @@
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
         <v>9.4</v>
@@ -2835,32 +2835,32 @@
         <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BG12" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
         <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3106,16 +3106,16 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
         <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q14" t="n">
         <v>1.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
@@ -3300,7 +3300,7 @@
         <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
         <v>4.9</v>
@@ -3315,10 +3315,10 @@
         <v>1.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
         <v>1.54</v>
@@ -3327,10 +3327,10 @@
         <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
         <v>28</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,7 +3497,7 @@
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
         <v>1.44</v>
@@ -3524,7 +3524,7 @@
         <v>1.18</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
         <v>12.5</v>
@@ -3551,7 +3551,7 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
@@ -3575,68 +3575,68 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW16" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF16" t="n">
         <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.23</v>
       </c>
       <c r="G17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H17" t="n">
         <v>14</v>
@@ -3682,13 +3682,13 @@
         <v>6.6</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
         <v>5.8</v>
@@ -3718,7 +3718,7 @@
         <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X17" t="n">
         <v>30</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>4.2</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H18" t="n">
         <v>1.81</v>
       </c>
       <c r="I18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J18" t="n">
         <v>3.9</v>
@@ -3885,7 +3885,7 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
@@ -3909,7 +3909,7 @@
         <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W18" t="n">
         <v>1.26</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G19" t="n">
         <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I19" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
@@ -4082,7 +4082,7 @@
         <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P19" t="n">
         <v>2.38</v>
@@ -4094,7 +4094,7 @@
         <v>1.65</v>
       </c>
       <c r="S19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
         <v>1.44</v>
@@ -4103,7 +4103,7 @@
         <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W19" t="n">
         <v>1.51</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4252,22 +4252,22 @@
         <v>2.96</v>
       </c>
       <c r="G20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
         <v>2.32</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J20" t="n">
         <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -4276,13 +4276,13 @@
         <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="R20" t="n">
         <v>1.37</v>
@@ -4291,19 +4291,19 @@
         <v>3.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U20" t="n">
         <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y20" t="n">
         <v>13.5</v>
@@ -4318,7 +4318,7 @@
         <v>16</v>
       </c>
       <c r="AC20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>14</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>3.15</v>
       </c>
       <c r="G21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H21" t="n">
         <v>2.02</v>
@@ -4461,7 +4461,7 @@
         <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
@@ -4494,7 +4494,7 @@
         <v>1.81</v>
       </c>
       <c r="W21" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X21" t="n">
         <v>30</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
         <v>5.7</v>
@@ -4676,7 +4676,7 @@
         <v>1.59</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="T22" t="n">
         <v>1.65</v>
@@ -4688,7 +4688,7 @@
         <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X22" t="n">
         <v>29</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
         <v>2.52</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R23" t="n">
         <v>1.61</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G24" t="n">
         <v>1.88</v>
@@ -5034,22 +5034,22 @@
         <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K24" t="n">
         <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.38</v>
@@ -5058,25 +5058,25 @@
         <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V24" t="n">
         <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X24" t="n">
         <v>13.5</v>
@@ -5085,7 +5085,7 @@
         <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA24" t="n">
         <v>130</v>
@@ -5106,7 +5106,7 @@
         <v>10.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
         <v>26</v>
@@ -5130,7 +5130,7 @@
         <v>14.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
@@ -5142,7 +5142,7 @@
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT24" t="n">
         <v>7.2</v>
@@ -5154,7 +5154,7 @@
         <v>17</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX24" t="n">
         <v>9.199999999999999</v>
@@ -5166,7 +5166,7 @@
         <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB24" t="n">
         <v>18.5</v>
@@ -5178,17 +5178,17 @@
         <v>36</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF24" t="n">
         <v>12.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G25" t="n">
         <v>1.6</v>
@@ -5231,73 +5231,73 @@
         <v>7.2</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V25" t="n">
         <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y25" t="n">
         <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="n">
         <v>110</v>
       </c>
       <c r="AF25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG25" t="n">
         <v>9.800000000000001</v>
@@ -5309,10 +5309,10 @@
         <v>110</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL25" t="n">
         <v>40</v>
@@ -5321,25 +5321,25 @@
         <v>160</v>
       </c>
       <c r="AN25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO25" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP25" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>50</v>
       </c>
       <c r="AS25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU25" t="n">
         <v>9</v>
@@ -5348,41 +5348,41 @@
         <v>24</v>
       </c>
       <c r="AW25" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AX25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BE25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G26" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
         <v>4</v>
@@ -5458,16 +5458,16 @@
         <v>1.73</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y26" t="n">
         <v>17</v>
@@ -5485,7 +5485,7 @@
         <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE26" t="n">
         <v>44</v>
@@ -5497,16 +5497,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
         <v>30</v>
@@ -5530,7 +5530,7 @@
         <v>29</v>
       </c>
       <c r="AS26" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AT26" t="n">
         <v>9.800000000000001</v>
@@ -5557,7 +5557,7 @@
         <v>46</v>
       </c>
       <c r="BB26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC26" t="n">
         <v>17</v>
@@ -5566,7 +5566,7 @@
         <v>27</v>
       </c>
       <c r="BE26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5643,7 +5643,7 @@
         <v>2.08</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
         <v>3.7</v>
@@ -5733,10 +5733,10 @@
         <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
@@ -5757,7 +5757,7 @@
         <v>17.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE27" t="n">
         <v>42</v>
@@ -5766,11 +5766,11 @@
         <v>11.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
         <v>80</v>
       </c>
       <c r="AN28" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO28" t="n">
         <v>28</v>
@@ -5933,7 +5933,7 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>11</v>
@@ -5954,17 +5954,17 @@
         <v>34</v>
       </c>
       <c r="BE28" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG28" t="n">
         <v>24</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H29" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I29" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J29" t="n">
         <v>3.55</v>
@@ -6043,10 +6043,10 @@
         <v>2.16</v>
       </c>
       <c r="V29" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X29" t="n">
         <v>18.5</v>
@@ -6076,7 +6076,7 @@
         <v>36</v>
       </c>
       <c r="AG29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH29" t="n">
         <v>22</v>
@@ -6124,13 +6124,13 @@
         <v>9.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX29" t="n">
         <v>4.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>15</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.18</v>
       </c>
       <c r="G30" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H30" t="n">
         <v>3.7</v>
@@ -6219,7 +6219,7 @@
         <v>1.38</v>
       </c>
       <c r="P30" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q30" t="n">
         <v>2.14</v>
@@ -6255,7 +6255,7 @@
         <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC30" t="n">
         <v>7.8</v>
@@ -6291,68 +6291,68 @@
         <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>60</v>
       </c>
       <c r="AP30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT30" t="n">
         <v>7.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX30" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.5</v>
       </c>
       <c r="AY30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD30" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG30" t="n">
         <v>6</v>
       </c>
-      <c r="BF30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         <v>8.4</v>
       </c>
       <c r="J31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K31" t="n">
         <v>5.4</v>
@@ -6416,13 +6416,13 @@
         <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S31" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
         <v>1.9</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="AI31" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ31" t="n">
         <v>12.5</v>
@@ -6485,10 +6485,10 @@
         <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO31" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP31" t="n">
         <v>17.5</v>
@@ -6497,22 +6497,22 @@
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU31" t="n">
         <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>8.199999999999999</v>
@@ -6524,7 +6524,7 @@
         <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB31" t="n">
         <v>11.5</v>
@@ -6536,17 +6536,17 @@
         <v>29</v>
       </c>
       <c r="BE31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF31" t="n">
         <v>5.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G33" t="n">
         <v>1.74</v>
       </c>
-      <c r="G33" t="n">
-        <v>1.76</v>
-      </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I33" t="n">
         <v>5.5</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K33" t="n">
         <v>4.4</v>
@@ -6801,19 +6801,19 @@
         <v>1.32</v>
       </c>
       <c r="P33" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R33" t="n">
         <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U33" t="n">
         <v>2</v>
@@ -6822,28 +6822,28 @@
         <v>1.22</v>
       </c>
       <c r="W33" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y33" t="n">
         <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA33" t="n">
         <v>140</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE33" t="n">
         <v>75</v>
@@ -6852,10 +6852,10 @@
         <v>10.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
         <v>80</v>
@@ -6870,25 +6870,25 @@
         <v>36</v>
       </c>
       <c r="AM33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN33" t="n">
         <v>11.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP33" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="AQ33" t="n">
         <v>15.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="AS33" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT33" t="n">
         <v>7.6</v>
@@ -6900,7 +6900,7 @@
         <v>18</v>
       </c>
       <c r="AW33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AX33" t="n">
         <v>9.4</v>
@@ -6909,32 +6909,32 @@
         <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BB33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC33" t="n">
         <v>16.5</v>
       </c>
-      <c r="BC33" t="n">
-        <v>14</v>
-      </c>
       <c r="BD33" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE33" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BF33" t="n">
         <v>10</v>
       </c>
       <c r="BG33" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -6977,10 +6977,10 @@
         <v>4.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K34" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L34" t="n">
         <v>1.36</v>
@@ -7013,7 +7013,7 @@
         <v>2.02</v>
       </c>
       <c r="V34" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W34" t="n">
         <v>1.98</v>
@@ -7037,7 +7037,7 @@
         <v>8.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE34" t="n">
         <v>65</v>
@@ -7067,7 +7067,7 @@
         <v>130</v>
       </c>
       <c r="AN34" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO34" t="n">
         <v>75</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -7162,10 +7162,10 @@
         <v>11.5</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="H35" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I35" t="n">
         <v>1.29</v>
@@ -7174,7 +7174,7 @@
         <v>7.4</v>
       </c>
       <c r="K35" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7204,46 +7204,46 @@
         <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V35" t="n">
         <v>4.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Y35" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z35" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AB35" t="n">
         <v>60</v>
       </c>
       <c r="AC35" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF35" t="n">
         <v>140</v>
       </c>
       <c r="AG35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AH35" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI35" t="n">
         <v>32</v>
@@ -7252,7 +7252,7 @@
         <v>470</v>
       </c>
       <c r="AK35" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AL35" t="n">
         <v>140</v>
@@ -7267,10 +7267,10 @@
         <v>3.65</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR35" t="n">
         <v>8.6</v>
@@ -7279,10 +7279,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT35" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="AU35" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AV35" t="n">
         <v>10</v>
@@ -7291,38 +7291,38 @@
         <v>12</v>
       </c>
       <c r="AX35" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AY35" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AZ35" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BA35" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BB35" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BE35" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG35" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -7362,10 +7362,10 @@
         <v>4.4</v>
       </c>
       <c r="I36" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K36" t="n">
         <v>3.85</v>
@@ -7377,31 +7377,31 @@
         <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O36" t="n">
         <v>1.38</v>
       </c>
       <c r="P36" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R36" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T36" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="U36" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="V36" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W36" t="n">
         <v>1.98</v>
@@ -7416,52 +7416,52 @@
         <v>44</v>
       </c>
       <c r="AA36" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB36" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC36" t="n">
         <v>9.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE36" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF36" t="n">
         <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>26</v>
       </c>
-      <c r="AI36" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>28</v>
-      </c>
       <c r="AK36" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL36" t="n">
         <v>55</v>
       </c>
       <c r="AM36" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN36" t="n">
         <v>970</v>
       </c>
       <c r="AO36" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ36" t="n">
         <v>10.5</v>
@@ -7473,25 +7473,25 @@
         <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU36" t="n">
         <v>6</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW36" t="n">
         <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY36" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -7959,16 +7959,16 @@
         <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O39" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P39" t="n">
         <v>1.52</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R39" t="n">
         <v>1.18</v>
@@ -7992,7 +7992,7 @@
         <v>10.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z39" t="n">
         <v>29</v>
@@ -8007,16 +8007,16 @@
         <v>8.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE39" t="n">
         <v>70</v>
       </c>
       <c r="AF39" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG39" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH39" t="n">
         <v>27</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
         <v>4.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
@@ -8377,25 +8377,25 @@
         <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Z41" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AA41" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AB41" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC41" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD41" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE41" t="n">
         <v>22</v>
@@ -8428,7 +8428,7 @@
         <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AP41" t="n">
         <v>1.01</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -8517,13 +8517,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="H42" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="I42" t="n">
         <v>2.8</v>
@@ -8541,34 +8541,34 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O42" t="n">
         <v>1.35</v>
       </c>
       <c r="P42" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="R42" t="n">
         <v>1.18</v>
       </c>
       <c r="S42" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V42" t="n">
         <v>1.55</v>
       </c>
       <c r="W42" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -8714,10 +8714,10 @@
         <v>2.46</v>
       </c>
       <c r="G43" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H43" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I43" t="n">
         <v>3.15</v>
@@ -8729,25 +8729,25 @@
         <v>4.1</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="O43" t="n">
         <v>1.41</v>
       </c>
       <c r="P43" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
         <v>3.3</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -8914,16 +8914,16 @@
         <v>1.95</v>
       </c>
       <c r="I44" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="J44" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K44" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L44" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M44" t="n">
         <v>1.08</v>
@@ -8947,19 +8947,19 @@
         <v>3.65</v>
       </c>
       <c r="T44" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="U44" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V44" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="W44" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X44" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y44" t="n">
         <v>8.800000000000001</v>
@@ -8986,7 +8986,7 @@
         <v>38</v>
       </c>
       <c r="AG44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH44" t="n">
         <v>24</v>
@@ -9019,56 +9019,56 @@
         <v>6.8</v>
       </c>
       <c r="AR44" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT44" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU44" t="n">
         <v>7</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW44" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ44" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ44" t="n">
+      <c r="BA44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG44" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA44" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -763,7 +763,7 @@
         <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
         <v>3.45</v>
@@ -772,7 +772,7 @@
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
@@ -781,7 +781,7 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.26</v>
@@ -802,7 +802,7 @@
         <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
         <v>1.41</v>
@@ -841,7 +841,7 @@
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
         <v>48</v>
@@ -850,16 +850,16 @@
         <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
         <v>34</v>
@@ -874,7 +874,7 @@
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -886,7 +886,7 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
@@ -898,29 +898,29 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
         <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="I3" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -999,13 +999,13 @@
         <v>2.46</v>
       </c>
       <c r="V3" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Y3" t="n">
         <v>16.5</v>
@@ -1020,7 +1020,7 @@
         <v>28</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>13</v>
@@ -1041,7 +1041,7 @@
         <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AK3" t="n">
         <v>46</v>
@@ -1053,13 +1053,13 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO3" t="n">
         <v>8.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
@@ -1095,26 +1095,26 @@
         <v>18</v>
       </c>
       <c r="BB3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC3" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC3" t="n">
-        <v>5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
         <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1187,7 +1187,7 @@
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
@@ -1196,7 +1196,7 @@
         <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
@@ -1259,7 +1259,7 @@
         <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS4" t="n">
         <v>6</v>
@@ -1268,7 +1268,7 @@
         <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>14</v>
@@ -1295,7 +1295,7 @@
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
         <v>6</v>
@@ -1304,11 +1304,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G5" t="n">
         <v>1.95</v>
@@ -1366,7 +1366,7 @@
         <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
         <v>2.06</v>
@@ -1381,13 +1381,13 @@
         <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
         <v>2.04</v>
@@ -1405,19 +1405,19 @@
         <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12</v>
@@ -1426,7 +1426,7 @@
         <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
         <v>24</v>
@@ -1438,7 +1438,7 @@
         <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
         <v>12.5</v>
@@ -1450,19 +1450,19 @@
         <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU5" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
@@ -1471,13 +1471,13 @@
         <v>4.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
         <v>4.7</v>
@@ -1489,7 +1489,7 @@
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
         <v>4.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
         <v>2.88</v>
       </c>
       <c r="I6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1581,7 +1581,7 @@
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
         <v>1.59</v>
@@ -1593,7 +1593,7 @@
         <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
         <v>65</v>
@@ -1611,19 +1611,19 @@
         <v>42</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
         <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK6" t="n">
         <v>34</v>
@@ -1641,62 +1641,62 @@
         <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1727,25 +1727,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
         <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1778,7 +1778,7 @@
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1844,7 +1844,7 @@
         <v>4.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
         <v>3.45</v>
@@ -1868,7 +1868,7 @@
         <v>4.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
         <v>4.4</v>
@@ -1880,7 +1880,7 @@
         <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="BF7" t="n">
         <v>4.2</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -1933,19 +1933,19 @@
         <v>2.98</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.36</v>
@@ -1975,7 +1975,7 @@
         <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
         <v>11</v>
@@ -2038,7 +2038,7 @@
         <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7.8</v>
@@ -2062,29 +2062,29 @@
         <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8" t="n">
         <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>10.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I9" t="n">
         <v>1.52</v>
@@ -2142,7 +2142,7 @@
         <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
         <v>1.98</v>
@@ -2151,7 +2151,7 @@
         <v>1.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
         <v>3.2</v>
@@ -2163,19 +2163,19 @@
         <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>970</v>
@@ -2208,7 +2208,7 @@
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AL9" t="n">
         <v>150</v>
@@ -2223,13 +2223,13 @@
         <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>4.7</v>
@@ -2244,7 +2244,7 @@
         <v>7.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
         <v>5.1</v>
@@ -2256,16 +2256,16 @@
         <v>4.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC9" t="n">
         <v>5.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
         <v>5.3</v>
@@ -2274,11 +2274,11 @@
         <v>5.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2333,22 +2333,22 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
         <v>1.05</v>
       </c>
       <c r="P10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q10" t="n">
         <v>1.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2527,19 +2527,19 @@
         <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O11" t="n">
         <v>1.07</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q11" t="n">
         <v>1.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S11" t="n">
         <v>1.9</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
         <v>2.98</v>
       </c>
       <c r="H12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I12" t="n">
         <v>3.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
@@ -2763,7 +2763,7 @@
         <v>75</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC12" t="n">
         <v>7.4</v>
@@ -2799,34 +2799,34 @@
         <v>230</v>
       </c>
       <c r="AN12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
         <v>80</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>6.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -2838,29 +2838,29 @@
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB12" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB12" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
         <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
         <v>3.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>3.85</v>
@@ -2924,16 +2924,16 @@
         <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
         <v>2.14</v>
@@ -2978,7 +2978,7 @@
         <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
         <v>34</v>
@@ -2990,7 +2990,7 @@
         <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN13" t="n">
         <v>19.5</v>
@@ -3008,7 +3008,7 @@
         <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
         <v>8.199999999999999</v>
@@ -3020,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX13" t="n">
         <v>11.5</v>
@@ -3032,29 +3032,29 @@
         <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC13" t="n">
         <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
         <v>12.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H14" t="n">
         <v>3.55</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3118,13 +3118,13 @@
         <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
         <v>1.6</v>
@@ -3133,122 +3133,122 @@
         <v>2.32</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.18</v>
+        <v>15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.18</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.14</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.18</v>
+        <v>9</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.18</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.18</v>
+        <v>3.9</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.18</v>
+        <v>11.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.18</v>
+        <v>3.95</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.18</v>
+        <v>17.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.18</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.14</v>
+        <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.18</v>
+        <v>3.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="G15" t="n">
         <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="I15" t="n">
         <v>1.77</v>
@@ -3312,7 +3312,7 @@
         <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R15" t="n">
         <v>1.49</v>
@@ -3333,7 +3333,7 @@
         <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
         <v>970</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3476,28 +3476,28 @@
         <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I16" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.22</v>
@@ -3506,13 +3506,13 @@
         <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="R16" t="n">
         <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
         <v>1.56</v>
@@ -3521,10 +3521,10 @@
         <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X16" t="n">
         <v>26</v>
@@ -3590,7 +3590,7 @@
         <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -3614,19 +3614,19 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC16" t="n">
         <v>18</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF16" t="n">
         <v>11.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.3</v>
@@ -3715,10 +3715,10 @@
         <v>2.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
@@ -3745,7 +3745,7 @@
         <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG17" t="n">
         <v>13</v>
@@ -3763,16 +3763,16 @@
         <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
         <v>80</v>
       </c>
       <c r="AN17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AP17" t="n">
         <v>16</v>
@@ -3784,7 +3784,7 @@
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT17" t="n">
         <v>9.800000000000001</v>
@@ -3796,7 +3796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX17" t="n">
         <v>13</v>
@@ -3808,16 +3808,16 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
         <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE17" t="n">
         <v>5.1</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I18" t="n">
         <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.28</v>
@@ -3885,13 +3885,13 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
         <v>1.7</v>
@@ -3903,10 +3903,10 @@
         <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V18" t="n">
         <v>1.44</v>
@@ -3924,7 +3924,7 @@
         <v>30</v>
       </c>
       <c r="AA18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
         <v>15.5</v>
@@ -3969,7 +3969,7 @@
         <v>29</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ18" t="n">
         <v>13</v>
@@ -3996,13 +3996,13 @@
         <v>14</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB18" t="n">
         <v>5.1</v>
@@ -4011,7 +4011,7 @@
         <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE18" t="n">
         <v>5.6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M19" t="n">
         <v>1.09</v>
       </c>
-      <c r="G19" t="n">
-        <v>970</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I19" t="n">
-        <v>970</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K19" t="n">
-        <v>950</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="N19" t="n">
-        <v>1.32</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
         <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.94</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="I20" t="n">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.33</v>
@@ -4273,146 +4273,146 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
         <v>1.67</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
         <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AB20" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
         <v>95</v>
       </c>
       <c r="AN20" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>11</v>
       </c>
       <c r="AS20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
         <v>19</v>
       </c>
       <c r="AX20" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="BG20" t="n">
         <v>13</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H21" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I21" t="n">
         <v>3.35</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
@@ -4476,22 +4476,22 @@
         <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
         <v>2.48</v>
       </c>
       <c r="T21" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="U21" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
         <v>1.67</v>
@@ -4560,7 +4560,7 @@
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT21" t="n">
         <v>10.5</v>
@@ -4572,7 +4572,7 @@
         <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX21" t="n">
         <v>13</v>
@@ -4584,19 +4584,19 @@
         <v>11</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC21" t="n">
         <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF21" t="n">
         <v>9.800000000000001</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
         <v>2.12</v>
@@ -4649,7 +4649,7 @@
         <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
         <v>3.65</v>
@@ -4697,7 +4697,7 @@
         <v>14.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
         <v>110</v>
@@ -4754,7 +4754,7 @@
         <v>5.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
@@ -4787,7 +4787,7 @@
         <v>5.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE22" t="n">
         <v>6.4</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="K23" t="n">
         <v>7.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
@@ -4861,7 +4861,7 @@
         <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q23" t="n">
         <v>1.38</v>
@@ -4870,19 +4870,19 @@
         <v>1.96</v>
       </c>
       <c r="S23" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="T23" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V23" t="n">
         <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X23" t="n">
         <v>140</v>
@@ -4894,7 +4894,7 @@
         <v>120</v>
       </c>
       <c r="AA23" t="n">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AB23" t="n">
         <v>15</v>
@@ -4903,7 +4903,7 @@
         <v>17.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE23" t="n">
         <v>150</v>
@@ -4927,7 +4927,7 @@
         <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4951,7 +4951,7 @@
         <v>55</v>
       </c>
       <c r="AT23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
         <v>15</v>
@@ -4972,7 +4972,7 @@
         <v>18</v>
       </c>
       <c r="BA23" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -4987,14 +4987,14 @@
         <v>38</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG23" t="n">
         <v>40</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
         <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T24" t="n">
         <v>1.72</v>
@@ -5076,7 +5076,7 @@
         <v>1.71</v>
       </c>
       <c r="W24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X24" t="n">
         <v>970</v>
@@ -5088,7 +5088,7 @@
         <v>970</v>
       </c>
       <c r="AA24" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB24" t="n">
         <v>970</v>
@@ -5142,7 +5142,7 @@
         <v>11.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT24" t="n">
         <v>10.5</v>
@@ -5154,10 +5154,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY24" t="n">
         <v>11</v>
@@ -5166,29 +5166,29 @@
         <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5252,13 +5252,13 @@
         <v>1.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
         <v>1.9</v>
@@ -5294,7 +5294,7 @@
         <v>17.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF25" t="n">
         <v>19.5</v>
@@ -5309,7 +5309,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK25" t="n">
         <v>42</v>
@@ -5336,7 +5336,7 @@
         <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT25" t="n">
         <v>6.6</v>
@@ -5348,7 +5348,7 @@
         <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
@@ -5360,29 +5360,29 @@
         <v>14.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG25" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>4</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G26" t="n">
         <v>1.91</v>
@@ -5428,22 +5428,22 @@
         <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
         <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q26" t="n">
         <v>2.24</v>
@@ -5476,7 +5476,7 @@
         <v>55</v>
       </c>
       <c r="AA26" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB26" t="n">
         <v>970</v>
@@ -5497,40 +5497,40 @@
         <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI26" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ26" t="n">
         <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM26" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
         <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT26" t="n">
         <v>5.8</v>
@@ -5539,44 +5539,44 @@
         <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX26" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB26" t="n">
         <v>4.1</v>
       </c>
-      <c r="BA26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.21</v>
       </c>
       <c r="G27" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="H27" t="n">
         <v>15.5</v>
@@ -5637,10 +5637,10 @@
         <v>1.16</v>
       </c>
       <c r="P27" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R27" t="n">
         <v>1.69</v>
@@ -5649,7 +5649,7 @@
         <v>2.18</v>
       </c>
       <c r="T27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U27" t="n">
         <v>1.77</v>
@@ -5685,7 +5685,7 @@
         <v>280</v>
       </c>
       <c r="AF27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
@@ -5697,34 +5697,34 @@
         <v>200</v>
       </c>
       <c r="AJ27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AK27" t="n">
         <v>14.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM27" t="n">
         <v>190</v>
       </c>
       <c r="AN27" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AO27" t="n">
         <v>440</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ27" t="n">
         <v>38</v>
       </c>
       <c r="AR27" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
@@ -5733,10 +5733,10 @@
         <v>13</v>
       </c>
       <c r="AV27" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>7.2</v>
@@ -5745,10 +5745,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB27" t="n">
         <v>8</v>
@@ -5757,20 +5757,20 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>29</v>
+        <v>8.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF27" t="n">
         <v>3.3</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
         <v>1.94</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K28" t="n">
         <v>4.3</v>
@@ -5909,7 +5909,7 @@
         <v>12</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ28" t="n">
         <v>9</v>
@@ -5918,10 +5918,10 @@
         <v>10.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AU28" t="n">
         <v>8.199999999999999</v>
@@ -5930,41 +5930,41 @@
         <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.95</v>
+        <v>15.5</v>
       </c>
       <c r="AX28" t="n">
         <v>4.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB28" t="n">
         <v>4.8</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE28" t="n">
         <v>4.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG28" t="n">
         <v>7.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G29" t="n">
         <v>3.8</v>
       </c>
       <c r="H29" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="I29" t="n">
         <v>2.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K29" t="n">
         <v>4.5</v>
@@ -6028,7 +6028,7 @@
         <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R29" t="n">
         <v>1.59</v>
@@ -6037,7 +6037,7 @@
         <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="U29" t="n">
         <v>2.5</v>
@@ -6112,7 +6112,7 @@
         <v>11.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AT29" t="n">
         <v>14</v>
@@ -6139,16 +6139,16 @@
         <v>20</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF29" t="n">
         <v>17.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6195,16 +6195,16 @@
         <v>2.82</v>
       </c>
       <c r="H30" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I30" t="n">
         <v>2.72</v>
       </c>
       <c r="J30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K30" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
         <v>1.23</v>
@@ -6297,7 +6297,7 @@
         <v>970</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AQ30" t="n">
         <v>13</v>
@@ -6306,7 +6306,7 @@
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT30" t="n">
         <v>13.5</v>
@@ -6318,10 +6318,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY30" t="n">
         <v>10</v>
@@ -6333,16 +6333,16 @@
         <v>21</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BF30" t="n">
         <v>10.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G31" t="n">
         <v>1.73</v>
@@ -6392,7 +6392,7 @@
         <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J31" t="n">
         <v>4.4</v>
@@ -6407,7 +6407,7 @@
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
         <v>1.2</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6589,10 +6589,10 @@
         <v>3.35</v>
       </c>
       <c r="J32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K32" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
         <v>1.24</v>
@@ -6622,7 +6622,7 @@
         <v>1.48</v>
       </c>
       <c r="U32" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V32" t="n">
         <v>1.43</v>
@@ -6649,7 +6649,7 @@
         <v>12</v>
       </c>
       <c r="AD32" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE32" t="n">
         <v>32</v>
@@ -6661,19 +6661,19 @@
         <v>14</v>
       </c>
       <c r="AH32" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ32" t="n">
         <v>34</v>
       </c>
       <c r="AK32" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL32" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM32" t="n">
         <v>55</v>
@@ -6685,7 +6685,7 @@
         <v>18.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AQ32" t="n">
         <v>16.5</v>
@@ -6694,19 +6694,19 @@
         <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT32" t="n">
         <v>13.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV32" t="n">
         <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX32" t="n">
         <v>14.5</v>
@@ -6721,7 +6721,7 @@
         <v>24</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC32" t="n">
         <v>15.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6783,13 +6783,13 @@
         <v>2.5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
         <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
@@ -6813,10 +6813,10 @@
         <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="U33" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V33" t="n">
         <v>1.66</v>
@@ -6828,22 +6828,22 @@
         <v>16.5</v>
       </c>
       <c r="Y33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD33" t="n">
         <v>13.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>14</v>
       </c>
       <c r="AE33" t="n">
         <v>32</v>
@@ -6852,31 +6852,31 @@
         <v>27</v>
       </c>
       <c r="AG33" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ33" t="n">
         <v>65</v>
       </c>
       <c r="AK33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
       </c>
       <c r="AM33" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN33" t="n">
         <v>32</v>
       </c>
       <c r="AO33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP33" t="n">
         <v>12</v>
@@ -6888,13 +6888,13 @@
         <v>12</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
         <v>8.4</v>
@@ -6912,19 +6912,19 @@
         <v>12</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF33" t="n">
         <v>21</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6965,25 +6965,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
@@ -6995,64 +6995,64 @@
         <v>1.38</v>
       </c>
       <c r="P34" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S34" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T34" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U34" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="V34" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="X34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y34" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y34" t="n">
-        <v>14</v>
-      </c>
       <c r="Z34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA34" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AE34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI34" t="n">
         <v>75</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>80</v>
       </c>
       <c r="AJ34" t="n">
         <v>25</v>
@@ -7061,74 +7061,74 @@
         <v>22</v>
       </c>
       <c r="AL34" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM34" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO34" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AP34" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ34" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR34" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS34" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AT34" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV34" t="n">
         <v>15</v>
       </c>
       <c r="AW34" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY34" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA34" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC34" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD34" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE34" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE34" t="n">
-        <v>12</v>
-      </c>
       <c r="BF34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G35" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="H35" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J35" t="n">
         <v>4.3</v>
@@ -7201,16 +7201,16 @@
         <v>3.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U35" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V35" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W35" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="X35" t="n">
         <v>14.5</v>
@@ -7225,10 +7225,10 @@
         <v>210</v>
       </c>
       <c r="AB35" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD35" t="n">
         <v>26</v>
@@ -7237,7 +7237,7 @@
         <v>110</v>
       </c>
       <c r="AF35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG35" t="n">
         <v>10</v>
@@ -7255,52 +7255,52 @@
         <v>17</v>
       </c>
       <c r="AL35" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM35" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO35" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP35" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>18</v>
       </c>
       <c r="AR35" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AS35" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU35" t="n">
         <v>9</v>
       </c>
       <c r="AV35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW35" t="n">
         <v>38</v>
       </c>
       <c r="AX35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY35" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA35" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BB35" t="n">
         <v>13</v>
@@ -7309,7 +7309,7 @@
         <v>16</v>
       </c>
       <c r="BD35" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BE35" t="n">
         <v>44</v>
@@ -7318,11 +7318,11 @@
         <v>8.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H36" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J36" t="n">
         <v>3.8</v>
       </c>
       <c r="K36" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.22</v>
@@ -7377,37 +7377,37 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="O36" t="n">
         <v>1.15</v>
       </c>
       <c r="P36" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R36" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="S36" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="T36" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U36" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W36" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X36" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y36" t="n">
         <v>26</v>
@@ -7416,13 +7416,13 @@
         <v>36</v>
       </c>
       <c r="AA36" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB36" t="n">
         <v>970</v>
       </c>
       <c r="AC36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD36" t="n">
         <v>970</v>
@@ -7431,92 +7431,92 @@
         <v>38</v>
       </c>
       <c r="AF36" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH36" t="n">
         <v>970</v>
       </c>
       <c r="AI36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM36" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN36" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AO36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AS36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC36" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY36" t="n">
+      <c r="BD36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF36" t="n">
         <v>3.7</v>
       </c>
-      <c r="AZ36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BG36" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -7550,19 +7550,19 @@
         <v>1.86</v>
       </c>
       <c r="G37" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K37" t="n">
         <v>4.2</v>
-      </c>
-      <c r="K37" t="n">
-        <v>4.3</v>
       </c>
       <c r="L37" t="n">
         <v>1.36</v>
@@ -7580,28 +7580,28 @@
         <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R37" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T37" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U37" t="n">
         <v>2.28</v>
       </c>
       <c r="V37" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W37" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X37" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y37" t="n">
         <v>17.5</v>
@@ -7610,10 +7610,10 @@
         <v>34</v>
       </c>
       <c r="AA37" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB37" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC37" t="n">
         <v>9.4</v>
@@ -7631,7 +7631,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH37" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI37" t="n">
         <v>55</v>
@@ -7643,61 +7643,61 @@
         <v>17.5</v>
       </c>
       <c r="AL37" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM37" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO37" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP37" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR37" t="n">
         <v>30</v>
       </c>
       <c r="AS37" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AT37" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU37" t="n">
         <v>9</v>
       </c>
       <c r="AV37" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AX37" t="n">
         <v>11</v>
       </c>
       <c r="AY37" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA37" t="n">
         <v>48</v>
       </c>
       <c r="BB37" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC37" t="n">
         <v>16.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BE37" t="n">
         <v>70</v>
@@ -7706,11 +7706,11 @@
         <v>10</v>
       </c>
       <c r="BG37" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>3.9</v>
       </c>
       <c r="L38" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M38" t="n">
         <v>1.08</v>
@@ -7771,7 +7771,7 @@
         <v>1.35</v>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
         <v>2.04</v>
@@ -7780,7 +7780,7 @@
         <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T38" t="n">
         <v>1.96</v>
@@ -7798,31 +7798,31 @@
         <v>13</v>
       </c>
       <c r="Y38" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA38" t="n">
         <v>140</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC38" t="n">
         <v>8.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE38" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG38" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH38" t="n">
         <v>22</v>
@@ -7834,13 +7834,13 @@
         <v>19</v>
       </c>
       <c r="AK38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL38" t="n">
         <v>38</v>
       </c>
       <c r="AM38" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN38" t="n">
         <v>13</v>
@@ -7861,7 +7861,7 @@
         <v>42</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU38" t="n">
         <v>7.8</v>
@@ -7870,41 +7870,41 @@
         <v>19</v>
       </c>
       <c r="AW38" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY38" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ38" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA38" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD38" t="n">
         <v>36</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>34</v>
       </c>
       <c r="BE38" t="n">
         <v>110</v>
       </c>
       <c r="BF38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG38" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G39" t="n">
         <v>2.54</v>
       </c>
       <c r="H39" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I39" t="n">
         <v>3.2</v>
       </c>
       <c r="J39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K39" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L39" t="n">
         <v>1.39</v>
@@ -7959,7 +7959,7 @@
         <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O39" t="n">
         <v>1.29</v>
@@ -7968,22 +7968,22 @@
         <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R39" t="n">
         <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T39" t="n">
         <v>1.73</v>
       </c>
       <c r="U39" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V39" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W39" t="n">
         <v>1.64</v>
@@ -7992,10 +7992,10 @@
         <v>14.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA39" t="n">
         <v>50</v>
@@ -8004,10 +8004,10 @@
         <v>12</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE39" t="n">
         <v>34</v>
@@ -8019,7 +8019,7 @@
         <v>12.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI39" t="n">
         <v>42</v>
@@ -8034,22 +8034,22 @@
         <v>38</v>
       </c>
       <c r="AM39" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN39" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO39" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP39" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>12.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS39" t="n">
         <v>44</v>
@@ -8058,10 +8058,10 @@
         <v>11</v>
       </c>
       <c r="AU39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW39" t="n">
         <v>30</v>
@@ -8073,7 +8073,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ39" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA39" t="n">
         <v>38</v>
@@ -8091,14 +8091,14 @@
         <v>70</v>
       </c>
       <c r="BF39" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H40" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I40" t="n">
         <v>2.08</v>
       </c>
       <c r="J40" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K40" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L40" t="n">
         <v>1.32</v>
@@ -8177,10 +8177,10 @@
         <v>2.18</v>
       </c>
       <c r="V40" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W40" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X40" t="n">
         <v>18.5</v>
@@ -8189,7 +8189,7 @@
         <v>11.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA40" t="n">
         <v>29</v>
@@ -8198,13 +8198,13 @@
         <v>18</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF40" t="n">
         <v>36</v>
@@ -8213,7 +8213,7 @@
         <v>18.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI40" t="n">
         <v>44</v>
@@ -8246,7 +8246,7 @@
         <v>11.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT40" t="n">
         <v>13</v>
@@ -8258,10 +8258,10 @@
         <v>9.4</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AY40" t="n">
         <v>14</v>
@@ -8270,19 +8270,19 @@
         <v>15</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC40" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>4.9</v>
       </c>
       <c r="BD40" t="n">
         <v>44</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF40" t="n">
         <v>34</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -8326,25 +8326,25 @@
         <v>2.18</v>
       </c>
       <c r="G41" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H41" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I41" t="n">
         <v>4.1</v>
       </c>
       <c r="J41" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K41" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N41" t="n">
         <v>3.25</v>
@@ -8353,16 +8353,16 @@
         <v>1.38</v>
       </c>
       <c r="P41" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R41" t="n">
         <v>1.29</v>
       </c>
       <c r="S41" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
         <v>1.87</v>
@@ -8371,22 +8371,22 @@
         <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W41" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X41" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y41" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z41" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA41" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB41" t="n">
         <v>9</v>
@@ -8395,16 +8395,16 @@
         <v>7.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE41" t="n">
         <v>55</v>
       </c>
       <c r="AF41" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH41" t="n">
         <v>21</v>
@@ -8413,10 +8413,10 @@
         <v>70</v>
       </c>
       <c r="AJ41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK41" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL41" t="n">
         <v>50</v>
@@ -8425,7 +8425,7 @@
         <v>130</v>
       </c>
       <c r="AN41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="n">
         <v>65</v>
@@ -8434,13 +8434,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="AS41" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AT41" t="n">
         <v>7.8</v>
@@ -8449,44 +8449,44 @@
         <v>6.8</v>
       </c>
       <c r="AV41" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ41" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA41" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="BC41" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BE41" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="BG41" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G42" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H42" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J42" t="n">
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L42" t="n">
         <v>1.27</v>
@@ -8559,28 +8559,28 @@
         <v>2.7</v>
       </c>
       <c r="T42" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U42" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W42" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X42" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y42" t="n">
         <v>32</v>
       </c>
       <c r="Z42" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA42" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="AB42" t="n">
         <v>12</v>
@@ -8589,22 +8589,22 @@
         <v>11.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE42" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG42" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH42" t="n">
         <v>24</v>
       </c>
       <c r="AI42" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ42" t="n">
         <v>12.5</v>
@@ -8616,7 +8616,7 @@
         <v>40</v>
       </c>
       <c r="AM42" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN42" t="n">
         <v>6.4</v>
@@ -8631,13 +8631,13 @@
         <v>24</v>
       </c>
       <c r="AR42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS42" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS42" t="n">
-        <v>10</v>
-      </c>
       <c r="AT42" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU42" t="n">
         <v>10</v>
@@ -8646,10 +8646,10 @@
         <v>25</v>
       </c>
       <c r="AW42" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AX42" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY42" t="n">
         <v>9.199999999999999</v>
@@ -8658,7 +8658,7 @@
         <v>20</v>
       </c>
       <c r="BA42" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BB42" t="n">
         <v>11.5</v>
@@ -8670,17 +8670,17 @@
         <v>29</v>
       </c>
       <c r="BE42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF42" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G43" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H43" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J43" t="n">
         <v>3.9</v>
@@ -8729,7 +8729,7 @@
         <v>4.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M43" t="n">
         <v>1.06</v>
@@ -8753,16 +8753,16 @@
         <v>3.15</v>
       </c>
       <c r="T43" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U43" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W43" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X43" t="n">
         <v>18.5</v>
@@ -8804,7 +8804,7 @@
         <v>22</v>
       </c>
       <c r="AK43" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AL43" t="n">
         <v>36</v>
@@ -8828,7 +8828,7 @@
         <v>5.7</v>
       </c>
       <c r="AS43" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT43" t="n">
         <v>8</v>
@@ -8837,7 +8837,7 @@
         <v>7.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW43" t="n">
         <v>5.9</v>
@@ -8861,20 +8861,20 @@
         <v>15.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE43" t="n">
         <v>6</v>
       </c>
       <c r="BF43" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG43" t="n">
         <v>6</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G44" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I44" t="n">
         <v>5.4</v>
       </c>
       <c r="J44" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L44" t="n">
         <v>1.35</v>
@@ -8929,7 +8929,7 @@
         <v>1.06</v>
       </c>
       <c r="N44" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
         <v>1.33</v>
@@ -8938,25 +8938,25 @@
         <v>1.98</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S44" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U44" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V44" t="n">
         <v>1.23</v>
       </c>
       <c r="W44" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X44" t="n">
         <v>15</v>
@@ -8965,10 +8965,10 @@
         <v>21</v>
       </c>
       <c r="Z44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA44" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB44" t="n">
         <v>8.4</v>
@@ -8986,13 +8986,13 @@
         <v>10.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH44" t="n">
         <v>22</v>
       </c>
       <c r="AI44" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="n">
         <v>18.5</v>
@@ -9010,19 +9010,19 @@
         <v>11.5</v>
       </c>
       <c r="AO44" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="n">
         <v>14</v>
       </c>
       <c r="AQ44" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR44" t="n">
         <v>12.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT44" t="n">
         <v>7.6</v>
@@ -9034,19 +9034,19 @@
         <v>18</v>
       </c>
       <c r="AW44" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX44" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY44" t="n">
         <v>9</v>
       </c>
       <c r="AZ44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB44" t="n">
         <v>14.5</v>
@@ -9058,17 +9058,17 @@
         <v>30</v>
       </c>
       <c r="BE44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF44" t="n">
         <v>10</v>
       </c>
       <c r="BG44" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -9099,19 +9099,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="G45" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="H45" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I45" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K45" t="n">
         <v>3.7</v>
@@ -9129,7 +9129,7 @@
         <v>1.36</v>
       </c>
       <c r="P45" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q45" t="n">
         <v>2.06</v>
@@ -9141,19 +9141,19 @@
         <v>3.6</v>
       </c>
       <c r="T45" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U45" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W45" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y45" t="n">
         <v>15</v>
@@ -9162,16 +9162,16 @@
         <v>32</v>
       </c>
       <c r="AA45" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB45" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD45" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE45" t="n">
         <v>65</v>
@@ -9180,13 +9180,13 @@
         <v>12.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH45" t="n">
         <v>20</v>
       </c>
       <c r="AI45" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="n">
         <v>24</v>
@@ -9198,13 +9198,13 @@
         <v>42</v>
       </c>
       <c r="AM45" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN45" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AO45" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP45" t="n">
         <v>11</v>
@@ -9213,56 +9213,56 @@
         <v>13.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AS45" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AT45" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU45" t="n">
         <v>7.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX45" t="n">
         <v>10</v>
       </c>
       <c r="AY45" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ45" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB45" t="n">
         <v>20</v>
       </c>
       <c r="BC45" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD45" t="n">
         <v>34</v>
       </c>
       <c r="BE45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF45" t="n">
         <v>13.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -9293,40 +9293,40 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G46" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H46" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="I46" t="n">
         <v>1.29</v>
       </c>
       <c r="J46" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
         <v>7.6</v>
       </c>
       <c r="L46" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M46" t="n">
         <v>1.02</v>
       </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O46" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R46" t="n">
         <v>1.82</v>
@@ -9335,31 +9335,31 @@
         <v>2.1</v>
       </c>
       <c r="T46" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="U46" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V46" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Y46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z46" t="n">
         <v>9.6</v>
       </c>
       <c r="AA46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AB46" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AC46" t="n">
         <v>16.5</v>
@@ -9368,10 +9368,10 @@
         <v>11</v>
       </c>
       <c r="AE46" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AF46" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AG46" t="n">
         <v>50</v>
@@ -9380,7 +9380,7 @@
         <v>32</v>
       </c>
       <c r="AI46" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ46" t="n">
         <v>470</v>
@@ -9398,25 +9398,25 @@
         <v>180</v>
       </c>
       <c r="AO46" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AP46" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AQ46" t="n">
         <v>11</v>
       </c>
       <c r="AR46" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS46" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT46" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AU46" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AV46" t="n">
         <v>10</v>
@@ -9425,7 +9425,7 @@
         <v>12</v>
       </c>
       <c r="AX46" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY46" t="n">
         <v>28</v>
@@ -9437,26 +9437,26 @@
         <v>26</v>
       </c>
       <c r="BB46" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BC46" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BE46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG46" t="n">
         <v>3.45</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G47" t="n">
         <v>1.85</v>
@@ -9502,7 +9502,7 @@
         <v>3.35</v>
       </c>
       <c r="K47" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L47" t="n">
         <v>1.44</v>
@@ -9526,7 +9526,7 @@
         <v>1.23</v>
       </c>
       <c r="S47" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T47" t="n">
         <v>2.12</v>
@@ -9565,7 +9565,7 @@
         <v>130</v>
       </c>
       <c r="AF47" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG47" t="n">
         <v>11</v>
@@ -9604,7 +9604,7 @@
         <v>8</v>
       </c>
       <c r="AS47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT47" t="n">
         <v>5.2</v>
@@ -9616,7 +9616,7 @@
         <v>20</v>
       </c>
       <c r="AW47" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX47" t="n">
         <v>7.4</v>
@@ -9625,10 +9625,10 @@
         <v>9</v>
       </c>
       <c r="AZ47" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA47" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB47" t="n">
         <v>15</v>
@@ -9637,20 +9637,20 @@
         <v>19.5</v>
       </c>
       <c r="BD47" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BE47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF47" t="n">
         <v>13</v>
       </c>
       <c r="BG47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
         <v>1.87</v>
       </c>
       <c r="G48" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H48" t="n">
         <v>4.5</v>
@@ -9693,19 +9693,19 @@
         <v>5.2</v>
       </c>
       <c r="J48" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K48" t="n">
         <v>3.75</v>
       </c>
       <c r="L48" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M48" t="n">
         <v>1.08</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O48" t="n">
         <v>1.38</v>
@@ -9732,10 +9732,10 @@
         <v>1.25</v>
       </c>
       <c r="W48" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X48" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y48" t="n">
         <v>970</v>
@@ -9759,7 +9759,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG48" t="n">
         <v>12.5</v>
@@ -9795,22 +9795,22 @@
         <v>10.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT48" t="n">
         <v>6</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV48" t="n">
         <v>14</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX48" t="n">
         <v>8.4</v>
@@ -9822,29 +9822,29 @@
         <v>15</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF48" t="n">
         <v>12</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9899,22 +9899,22 @@
         <v>1.07</v>
       </c>
       <c r="N49" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="O49" t="n">
         <v>1.32</v>
       </c>
       <c r="P49" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R49" t="n">
         <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T49" t="n">
         <v>1.01</v>
@@ -9923,13 +9923,13 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W49" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y49" t="n">
         <v>1000</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -10069,70 +10069,70 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G50" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H50" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K50" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L50" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M50" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N50" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
         <v>1.38</v>
       </c>
       <c r="P50" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R50" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T50" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U50" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V50" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W50" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X50" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y50" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z50" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA50" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB50" t="n">
         <v>10</v>
@@ -10141,10 +10141,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD50" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF50" t="n">
         <v>16</v>
@@ -10156,7 +10156,7 @@
         <v>22</v>
       </c>
       <c r="AI50" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ50" t="n">
         <v>34</v>
@@ -10165,74 +10165,74 @@
         <v>30</v>
       </c>
       <c r="AL50" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM50" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO50" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP50" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AQ50" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR50" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT50" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU50" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="AV50" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX50" t="n">
         <v>10.5</v>
       </c>
       <c r="AY50" t="n">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="AZ50" t="n">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC50" t="n">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF50" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G51" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="H51" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K51" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L51" t="n">
         <v>1.48</v>
@@ -10287,19 +10287,19 @@
         <v>1.1</v>
       </c>
       <c r="N51" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O51" t="n">
         <v>1.47</v>
       </c>
       <c r="P51" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q51" t="n">
         <v>2.4</v>
       </c>
       <c r="R51" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S51" t="n">
         <v>4.8</v>
@@ -10308,25 +10308,25 @@
         <v>2.06</v>
       </c>
       <c r="U51" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V51" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W51" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="X51" t="n">
         <v>11.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z51" t="n">
         <v>42</v>
       </c>
       <c r="AA51" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB51" t="n">
         <v>7.2</v>
@@ -10338,61 +10338,61 @@
         <v>970</v>
       </c>
       <c r="AE51" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF51" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG51" t="n">
         <v>11.5</v>
       </c>
       <c r="AH51" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK51" t="n">
         <v>29</v>
       </c>
-      <c r="AI51" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>30</v>
-      </c>
       <c r="AL51" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM51" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN51" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO51" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP51" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ51" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT51" t="n">
         <v>5</v>
       </c>
       <c r="AU51" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW51" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX51" t="n">
         <v>8.4</v>
@@ -10404,7 +10404,7 @@
         <v>18.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB51" t="n">
         <v>20</v>
@@ -10413,20 +10413,20 @@
         <v>19.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF51" t="n">
         <v>19</v>
       </c>
       <c r="BG51" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -10660,16 +10660,16 @@
         <v>1.7</v>
       </c>
       <c r="I53" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J53" t="n">
         <v>3.75</v>
       </c>
       <c r="K53" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L53" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M53" t="n">
         <v>1.08</v>
@@ -10699,7 +10699,7 @@
         <v>1.72</v>
       </c>
       <c r="V53" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W53" t="n">
         <v>1.2</v>
@@ -10759,62 +10759,62 @@
         <v>970</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BG53" t="n">
         <v>10.5</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -10845,16 +10845,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G54" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H54" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I54" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J54" t="n">
         <v>3.2</v>
@@ -10896,7 +10896,7 @@
         <v>1.56</v>
       </c>
       <c r="W54" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X54" t="n">
         <v>15</v>
@@ -10953,40 +10953,40 @@
         <v>36</v>
       </c>
       <c r="AP54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ54" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AR54" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AS54" t="n">
         <v>3.9</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AU54" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AV54" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AW54" t="n">
         <v>3.8</v>
       </c>
       <c r="AX54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ54" t="n">
         <v>3.6</v>
       </c>
-      <c r="AY54" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BA54" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB54" t="n">
         <v>4</v>
@@ -11001,14 +11001,14 @@
         <v>4.1</v>
       </c>
       <c r="BF54" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG54" t="n">
         <v>3.8</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11057,7 @@
         <v>3.65</v>
       </c>
       <c r="L55" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M55" t="n">
         <v>1.09</v>
@@ -11156,19 +11156,19 @@
         <v>13.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT55" t="n">
         <v>7</v>
       </c>
       <c r="AU55" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV55" t="n">
         <v>9.6</v>
       </c>
       <c r="AW55" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX55" t="n">
         <v>13</v>
@@ -11180,29 +11180,29 @@
         <v>14</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG55" t="n">
         <v>4.5</v>
       </c>
-      <c r="BF55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG55" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -11242,13 +11242,13 @@
         <v>1.93</v>
       </c>
       <c r="I56" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J56" t="n">
         <v>3.35</v>
       </c>
       <c r="K56" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L56" t="n">
         <v>1.44</v>
@@ -11272,16 +11272,16 @@
         <v>1.28</v>
       </c>
       <c r="S56" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T56" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U56" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V56" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W56" t="n">
         <v>1.26</v>
@@ -11350,7 +11350,7 @@
         <v>10</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AT56" t="n">
         <v>12</v>
@@ -11362,25 +11362,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX56" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY56" t="n">
         <v>15</v>
       </c>
       <c r="AZ56" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BA56" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB56" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC56" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>4.8</v>
       </c>
       <c r="BD56" t="n">
         <v>4.8</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
         <v>2.48</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
         <v>3.4</v>
@@ -772,28 +772,28 @@
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
         <v>2.92</v>
@@ -802,7 +802,7 @@
         <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
         <v>1.42</v>
@@ -832,7 +832,7 @@
         <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
         <v>18.5</v>
@@ -853,16 +853,16 @@
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AN2" t="n">
         <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
@@ -874,7 +874,7 @@
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -898,7 +898,7 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
         <v>14.5</v>
@@ -910,7 +910,7 @@
         <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
         <v>12.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I3" t="n">
         <v>1.83</v>
@@ -966,10 +966,10 @@
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -978,16 +978,16 @@
         <v>5.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
         <v>2.28</v>
@@ -1002,28 +1002,28 @@
         <v>2.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
         <v>48</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
         <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC3" t="n">
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
         <v>17.5</v>
@@ -1047,16 +1047,16 @@
         <v>100</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
@@ -1095,26 +1095,26 @@
         <v>18</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
         <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
         <v>12</v>
@@ -1253,40 +1253,40 @@
         <v>290</v>
       </c>
       <c r="AP4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
         <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
@@ -1295,20 +1295,20 @@
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
@@ -1372,7 +1372,7 @@
         <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
         <v>1.42</v>
@@ -1384,7 +1384,7 @@
         <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V5" t="n">
         <v>1.25</v>
@@ -1393,7 +1393,7 @@
         <v>2.02</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y5" t="n">
         <v>19</v>
@@ -1405,7 +1405,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
         <v>9.4</v>
@@ -1456,7 +1456,7 @@
         <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>8.6</v>
@@ -1468,7 +1468,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1480,7 +1480,7 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
         <v>15.5</v>
@@ -1492,7 +1492,7 @@
         <v>16</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
         <v>8.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.8</v>
@@ -1563,10 +1563,10 @@
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
@@ -1683,10 +1683,10 @@
         <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
         <v>15</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1757,16 +1757,16 @@
         <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
         <v>1.75</v>
@@ -1838,13 +1838,13 @@
         <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
         <v>4.9</v>
@@ -1856,7 +1856,7 @@
         <v>4.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX7" t="n">
         <v>6.2</v>
@@ -1865,32 +1865,32 @@
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC7" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
         <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1921,52 +1921,52 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>2.66</v>
       </c>
       <c r="I8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.06</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.08</v>
       </c>
       <c r="V8" t="n">
         <v>1.52</v>
@@ -1975,13 +1975,13 @@
         <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
         <v>500</v>
@@ -1990,10 +1990,10 @@
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>90</v>
@@ -2008,7 +2008,7 @@
         <v>42</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ8" t="n">
         <v>220</v>
@@ -2032,7 +2032,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
         <v>15.5</v>
@@ -2077,14 +2077,14 @@
         <v>11.5</v>
       </c>
       <c r="BF8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG8" t="n">
-        <v>9</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2118,22 +2118,22 @@
         <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="I9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2145,7 +2145,7 @@
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
         <v>1.79</v>
@@ -2157,13 +2157,13 @@
         <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="V9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="W9" t="n">
         <v>1.12</v>
@@ -2175,7 +2175,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
         <v>23</v>
@@ -2229,13 +2229,13 @@
         <v>4.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS9" t="n">
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
         <v>7.8</v>
@@ -2244,41 +2244,41 @@
         <v>7.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AZ9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE9" t="n">
         <v>6.4</v>
       </c>
-      <c r="BA9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
         <v>4.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2339,10 +2339,10 @@
         <v>1.04</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="R10" t="n">
         <v>1.07</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>110</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>8.4</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y11" t="n">
         <v>970</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>500</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -2572,16 +2572,16 @@
         <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
         <v>500</v>
@@ -2590,7 +2590,7 @@
         <v>500</v>
       </c>
       <c r="AI11" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
         <v>900</v>
@@ -2602,7 +2602,7 @@
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>500</v>
@@ -2614,59 +2614,59 @@
         <v>4.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.17</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.21</v>
+        <v>2.02</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.21</v>
+        <v>3.95</v>
       </c>
       <c r="AU11" t="n">
         <v>4.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.19</v>
+        <v>5.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.21</v>
+        <v>2.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.21</v>
+        <v>4.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.21</v>
+        <v>4.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.19</v>
+        <v>3.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.21</v>
+        <v>3.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.21</v>
+        <v>6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.21</v>
+        <v>3.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.21</v>
+        <v>2.44</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.21</v>
+        <v>3.65</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.21</v>
+        <v>4</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.66</v>
       </c>
       <c r="G12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
         <v>2.98</v>
@@ -2748,10 +2748,10 @@
         <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y12" t="n">
         <v>9.199999999999999</v>
@@ -2775,13 +2775,13 @@
         <v>120</v>
       </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="n">
         <v>210</v>
@@ -2808,13 +2808,13 @@
         <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2823,44 +2823,44 @@
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF12" t="n">
         <v>8</v>
       </c>
-      <c r="BD12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG12" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -2915,13 +2915,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
         <v>1.31</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>2.18</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3133,10 +3133,10 @@
         <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X14" t="n">
         <v>16.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G15" t="n">
         <v>2.16</v>
@@ -3288,7 +3288,7 @@
         <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
         <v>3.75</v>
@@ -3321,10 +3321,10 @@
         <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
         <v>1.31</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.31</v>
@@ -3497,34 +3497,34 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="T16" t="n">
         <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
         <v>42</v>
@@ -3539,16 +3539,16 @@
         <v>29</v>
       </c>
       <c r="AB16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
         <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
         <v>500</v>
@@ -3578,10 +3578,10 @@
         <v>700</v>
       </c>
       <c r="AO16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.4</v>
@@ -3596,7 +3596,7 @@
         <v>17</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>7.8</v>
@@ -3605,7 +3605,7 @@
         <v>12.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY16" t="n">
         <v>16</v>
@@ -3614,29 +3614,29 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3670,46 +3670,46 @@
         <v>2.48</v>
       </c>
       <c r="G17" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
         <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U17" t="n">
         <v>2.42</v>
@@ -3718,22 +3718,22 @@
         <v>1.52</v>
       </c>
       <c r="W17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
         <v>26</v>
       </c>
       <c r="AA17" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
         <v>11.5</v>
@@ -3757,7 +3757,7 @@
         <v>36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
         <v>32</v>
@@ -3784,7 +3784,7 @@
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT17" t="n">
         <v>12</v>
@@ -3796,7 +3796,7 @@
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
         <v>16.5</v>
@@ -3811,7 +3811,7 @@
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
@@ -3820,7 +3820,7 @@
         <v>16</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF17" t="n">
         <v>13.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3894,7 +3894,7 @@
         <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
         <v>1.47</v>
@@ -3906,13 +3906,13 @@
         <v>1.61</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
         <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -3924,13 +3924,13 @@
         <v>28</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
         <v>14</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>16</v>
@@ -3963,7 +3963,7 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>32</v>
@@ -3996,7 +3996,7 @@
         <v>13</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>12</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4121,7 +4121,7 @@
         <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC19" t="n">
         <v>9.199999999999999</v>
@@ -4172,7 +4172,7 @@
         <v>22</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
@@ -4193,13 +4193,13 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB19" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BC19" t="n">
         <v>19</v>
@@ -4214,11 +4214,11 @@
         <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4267,16 +4267,16 @@
         <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P20" t="n">
         <v>1.67</v>
@@ -4348,7 +4348,7 @@
         <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>38</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>3.15</v>
       </c>
       <c r="G21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H21" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I21" t="n">
         <v>2.38</v>
@@ -4458,10 +4458,10 @@
         <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -4494,7 +4494,7 @@
         <v>1.72</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X21" t="n">
         <v>17.5</v>
@@ -4509,16 +4509,16 @@
         <v>34</v>
       </c>
       <c r="AB21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC21" t="n">
         <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
@@ -4548,7 +4548,7 @@
         <v>36</v>
       </c>
       <c r="AO21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP21" t="n">
         <v>14.5</v>
@@ -4569,13 +4569,13 @@
         <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW21" t="n">
         <v>18</v>
       </c>
       <c r="AX21" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY21" t="n">
         <v>13</v>
@@ -4593,10 +4593,10 @@
         <v>25</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>19.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G22" t="n">
         <v>2.42</v>
       </c>
       <c r="H22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I22" t="n">
         <v>3.35</v>
@@ -4694,10 +4694,10 @@
         <v>27</v>
       </c>
       <c r="Y22" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -4706,10 +4706,10 @@
         <v>17</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
@@ -4724,16 +4724,16 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK22" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -4751,10 +4751,10 @@
         <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.5</v>
+        <v>32</v>
       </c>
       <c r="AT22" t="n">
         <v>10.5</v>
@@ -4766,7 +4766,7 @@
         <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
         <v>13</v>
@@ -4778,29 +4778,29 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BC22" t="n">
         <v>16</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G23" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
         <v>4.1</v>
@@ -4843,13 +4843,13 @@
         <v>4.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
         <v>3.65</v>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -4861,7 +4861,7 @@
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
         <v>2.1</v>
@@ -4876,13 +4876,13 @@
         <v>1.86</v>
       </c>
       <c r="U23" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="X23" t="n">
         <v>13.5</v>
@@ -4948,7 +4948,7 @@
         <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23" t="n">
         <v>7.6</v>
@@ -4981,20 +4981,20 @@
         <v>11.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF23" t="n">
         <v>15</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
         <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q24" t="n">
         <v>1.4</v>
@@ -5064,10 +5064,10 @@
         <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U24" t="n">
         <v>2.14</v>
@@ -5127,10 +5127,10 @@
         <v>320</v>
       </c>
       <c r="AN24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AO24" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP24" t="n">
         <v>34</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5219,67 +5219,67 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G25" t="n">
         <v>3.6</v>
       </c>
       <c r="H25" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I25" t="n">
         <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.34</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
         <v>3.65</v>
       </c>
       <c r="O25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
         <v>1.78</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V25" t="n">
         <v>1.71</v>
       </c>
       <c r="W25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
         <v>90</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -5336,7 +5336,7 @@
         <v>11.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT25" t="n">
         <v>10.5</v>
@@ -5348,10 +5348,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AY25" t="n">
         <v>11</v>
@@ -5360,29 +5360,29 @@
         <v>12.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG25" t="n">
         <v>4.7</v>
       </c>
-      <c r="BD25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.48</v>
       </c>
       <c r="G26" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H26" t="n">
         <v>3.05</v>
@@ -5431,7 +5431,7 @@
         <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
@@ -5455,7 +5455,7 @@
         <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U26" t="n">
         <v>1.9</v>
@@ -5509,10 +5509,10 @@
         <v>95</v>
       </c>
       <c r="AL26" t="n">
-        <v>65</v>
+        <v>460</v>
       </c>
       <c r="AM26" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
         <v>42</v>
@@ -5521,10 +5521,10 @@
         <v>180</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
         <v>18</v>
@@ -5533,50 +5533,50 @@
         <v>4.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
         <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY26" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="BC26" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="BD26" t="n">
         <v>4.7</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF26" t="n">
         <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G27" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I27" t="n">
         <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
         <v>3.8</v>
@@ -5643,7 +5643,7 @@
         <v>2.24</v>
       </c>
       <c r="R27" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
         <v>3.95</v>
@@ -5652,13 +5652,13 @@
         <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V27" t="n">
         <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X27" t="n">
         <v>11.5</v>
@@ -5700,7 +5700,7 @@
         <v>900</v>
       </c>
       <c r="AK27" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AL27" t="n">
         <v>500</v>
@@ -5715,19 +5715,19 @@
         <v>700</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AQ27" t="n">
         <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
@@ -5736,7 +5736,7 @@
         <v>11.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>8.199999999999999</v>
@@ -5748,29 +5748,29 @@
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB27" t="n">
         <v>9</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G28" t="n">
         <v>1.24</v>
@@ -5810,7 +5810,7 @@
         <v>15.5</v>
       </c>
       <c r="I28" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
         <v>7.4</v>
@@ -5819,7 +5819,7 @@
         <v>8.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M28" t="n">
         <v>1.03</v>
@@ -5831,7 +5831,7 @@
         <v>1.16</v>
       </c>
       <c r="P28" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="Q28" t="n">
         <v>1.48</v>
@@ -5840,19 +5840,19 @@
         <v>1.69</v>
       </c>
       <c r="S28" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
         <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X28" t="n">
         <v>42</v>
@@ -5894,7 +5894,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL28" t="n">
         <v>95</v>
@@ -5915,10 +5915,10 @@
         <v>38</v>
       </c>
       <c r="AR28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS28" t="n">
         <v>11</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>11.5</v>
       </c>
       <c r="AT28" t="n">
         <v>9</v>
@@ -5927,10 +5927,10 @@
         <v>15</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX28" t="n">
         <v>7.2</v>
@@ -5942,7 +5942,7 @@
         <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB28" t="n">
         <v>7.8</v>
@@ -5951,10 +5951,10 @@
         <v>12</v>
       </c>
       <c r="BD28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
         <v>3.35</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v>1.86</v>
       </c>
       <c r="I29" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J29" t="n">
         <v>3.8</v>
@@ -6040,10 +6040,10 @@
         <v>1.72</v>
       </c>
       <c r="U29" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V29" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W29" t="n">
         <v>1.28</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="G30" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.24</v>
@@ -6213,19 +6213,19 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
         <v>1.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S30" t="n">
         <v>2.4</v>
@@ -6234,13 +6234,13 @@
         <v>1.59</v>
       </c>
       <c r="U30" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="W30" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X30" t="n">
         <v>32</v>
@@ -6249,22 +6249,22 @@
         <v>22</v>
       </c>
       <c r="Z30" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AB30" t="n">
         <v>24</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE30" t="n">
-        <v>46</v>
+        <v>18.5</v>
       </c>
       <c r="AF30" t="n">
         <v>36</v>
@@ -6294,7 +6294,7 @@
         <v>30</v>
       </c>
       <c r="AO30" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AP30" t="n">
         <v>18</v>
@@ -6312,7 +6312,7 @@
         <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV30" t="n">
         <v>8.199999999999999</v>
@@ -6324,7 +6324,7 @@
         <v>21</v>
       </c>
       <c r="AY30" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AZ30" t="n">
         <v>11</v>
@@ -6333,7 +6333,7 @@
         <v>20</v>
       </c>
       <c r="BB30" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BC30" t="n">
         <v>16</v>
@@ -6342,17 +6342,17 @@
         <v>18</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>17.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG30" t="n">
         <v>7.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G32" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H32" t="n">
         <v>5</v>
@@ -6592,7 +6592,7 @@
         <v>4.4</v>
       </c>
       <c r="K32" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L32" t="n">
         <v>1.25</v>
@@ -6601,19 +6601,19 @@
         <v>1.03</v>
       </c>
       <c r="N32" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O32" t="n">
         <v>1.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q32" t="n">
         <v>1.56</v>
       </c>
       <c r="R32" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S32" t="n">
         <v>2.38</v>
@@ -6628,7 +6628,7 @@
         <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X32" t="n">
         <v>29</v>
@@ -6676,7 +6676,7 @@
         <v>32</v>
       </c>
       <c r="AM32" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN32" t="n">
         <v>7.8</v>
@@ -6694,7 +6694,7 @@
         <v>5.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT32" t="n">
         <v>9.4</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
         <v>3.75</v>
       </c>
       <c r="L34" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
         <v>1.06</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7162,16 +7162,16 @@
         <v>1.02</v>
       </c>
       <c r="G35" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I35" t="n">
         <v>990</v>
       </c>
       <c r="J35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K35" t="n">
         <v>950</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7359,13 +7359,13 @@
         <v>990</v>
       </c>
       <c r="H36" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I36" t="n">
         <v>990</v>
       </c>
       <c r="J36" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
@@ -7377,7 +7377,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7550,10 +7550,10 @@
         <v>2.04</v>
       </c>
       <c r="G37" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H37" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I37" t="n">
         <v>4.1</v>
@@ -7565,7 +7565,7 @@
         <v>3.95</v>
       </c>
       <c r="L37" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -7574,13 +7574,13 @@
         <v>3.4</v>
       </c>
       <c r="O37" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P37" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R37" t="n">
         <v>1.32</v>
@@ -7589,16 +7589,16 @@
         <v>3.85</v>
       </c>
       <c r="T37" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U37" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V37" t="n">
         <v>1.32</v>
       </c>
       <c r="W37" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X37" t="n">
         <v>16.5</v>
@@ -7610,7 +7610,7 @@
         <v>30</v>
       </c>
       <c r="AA37" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AB37" t="n">
         <v>8.4</v>
@@ -7634,7 +7634,7 @@
         <v>21</v>
       </c>
       <c r="AI37" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ37" t="n">
         <v>26</v>
@@ -7643,7 +7643,7 @@
         <v>22</v>
       </c>
       <c r="AL37" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AM37" t="n">
         <v>120</v>
@@ -7664,7 +7664,7 @@
         <v>14.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT37" t="n">
         <v>7.6</v>
@@ -7673,7 +7673,7 @@
         <v>7.8</v>
       </c>
       <c r="AV37" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW37" t="n">
         <v>23</v>
@@ -7688,7 +7688,7 @@
         <v>19</v>
       </c>
       <c r="BA37" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BB37" t="n">
         <v>23</v>
@@ -7700,17 +7700,17 @@
         <v>36</v>
       </c>
       <c r="BE37" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="BF37" t="n">
         <v>15.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O38" t="n">
         <v>1.32</v>
@@ -7777,7 +7777,7 @@
         <v>1.96</v>
       </c>
       <c r="R38" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S38" t="n">
         <v>3.5</v>
@@ -7786,7 +7786,7 @@
         <v>2.04</v>
       </c>
       <c r="U38" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V38" t="n">
         <v>1.17</v>
@@ -7798,7 +7798,7 @@
         <v>14.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z38" t="n">
         <v>55</v>
@@ -7810,7 +7810,7 @@
         <v>8</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD38" t="n">
         <v>25</v>
@@ -7828,7 +7828,7 @@
         <v>24</v>
       </c>
       <c r="AI38" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ38" t="n">
         <v>14.5</v>
@@ -7843,7 +7843,7 @@
         <v>140</v>
       </c>
       <c r="AN38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO38" t="n">
         <v>150</v>
@@ -7882,7 +7882,7 @@
         <v>21</v>
       </c>
       <c r="BA38" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BB38" t="n">
         <v>13</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>1.98</v>
       </c>
       <c r="G39" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="H39" t="n">
         <v>3.2</v>
@@ -7950,7 +7950,7 @@
         <v>3.8</v>
       </c>
       <c r="K39" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L39" t="n">
         <v>1.22</v>
@@ -7962,7 +7962,7 @@
         <v>1.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P39" t="n">
         <v>2.48</v>
@@ -7974,7 +7974,7 @@
         <v>1.69</v>
       </c>
       <c r="S39" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
         <v>1.45</v>
@@ -7986,7 +7986,7 @@
         <v>1.35</v>
       </c>
       <c r="W39" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="X39" t="n">
         <v>500</v>
@@ -8001,7 +8001,7 @@
         <v>900</v>
       </c>
       <c r="AB39" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AC39" t="n">
         <v>42</v>
@@ -8016,7 +8016,7 @@
         <v>970</v>
       </c>
       <c r="AG39" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AH39" t="n">
         <v>60</v>
@@ -8028,7 +8028,7 @@
         <v>900</v>
       </c>
       <c r="AK39" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AL39" t="n">
         <v>500</v>
@@ -8043,62 +8043,62 @@
         <v>500</v>
       </c>
       <c r="AP39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ39" t="n">
         <v>6</v>
       </c>
       <c r="AR39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV39" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>5.5</v>
       </c>
       <c r="AW39" t="n">
         <v>6.4</v>
       </c>
       <c r="AX39" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY39" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA39" t="n">
         <v>6.4</v>
       </c>
       <c r="BB39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF39" t="n">
         <v>4.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8132,19 +8132,19 @@
         <v>1.86</v>
       </c>
       <c r="G40" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I40" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="n">
         <v>4.1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4.2</v>
       </c>
       <c r="L40" t="n">
         <v>1.36</v>
@@ -8174,13 +8174,13 @@
         <v>1.76</v>
       </c>
       <c r="U40" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V40" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W40" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X40" t="n">
         <v>17.5</v>
@@ -8195,16 +8195,16 @@
         <v>95</v>
       </c>
       <c r="AB40" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC40" t="n">
         <v>9</v>
       </c>
       <c r="AD40" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF40" t="n">
         <v>12</v>
@@ -8213,13 +8213,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH40" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI40" t="n">
         <v>55</v>
       </c>
       <c r="AJ40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK40" t="n">
         <v>17.5</v>
@@ -8240,7 +8240,7 @@
         <v>17</v>
       </c>
       <c r="AQ40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR40" t="n">
         <v>30</v>
@@ -8258,7 +8258,7 @@
         <v>16.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX40" t="n">
         <v>11</v>
@@ -8273,10 +8273,10 @@
         <v>48</v>
       </c>
       <c r="BB40" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD40" t="n">
         <v>27</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v>5.1</v>
       </c>
       <c r="I41" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>3.85</v>
@@ -8347,7 +8347,7 @@
         <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O41" t="n">
         <v>1.36</v>
@@ -8356,7 +8356,7 @@
         <v>1.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R41" t="n">
         <v>1.33</v>
@@ -8404,7 +8404,7 @@
         <v>10</v>
       </c>
       <c r="AG41" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH41" t="n">
         <v>22</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G42" t="n">
         <v>2.52</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.54</v>
       </c>
       <c r="H42" t="n">
         <v>3.2</v>
       </c>
       <c r="I42" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
         <v>3.35</v>
@@ -8550,25 +8550,25 @@
         <v>2.02</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R42" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S42" t="n">
         <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U42" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V42" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W42" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X42" t="n">
         <v>14</v>
@@ -8649,7 +8649,7 @@
         <v>30</v>
       </c>
       <c r="AX42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY42" t="n">
         <v>11.5</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G43" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H43" t="n">
         <v>2.04</v>
@@ -8741,7 +8741,7 @@
         <v>1.3</v>
       </c>
       <c r="P43" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q43" t="n">
         <v>1.9</v>
@@ -8762,10 +8762,10 @@
         <v>1.92</v>
       </c>
       <c r="W43" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X43" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Y43" t="n">
         <v>11.5</v>
@@ -8780,7 +8780,7 @@
         <v>17</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43" t="n">
         <v>10.5</v>
@@ -8789,13 +8789,13 @@
         <v>23</v>
       </c>
       <c r="AF43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG43" t="n">
         <v>18</v>
       </c>
       <c r="AH43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI43" t="n">
         <v>44</v>
@@ -8816,7 +8816,7 @@
         <v>55</v>
       </c>
       <c r="AO43" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP43" t="n">
         <v>13.5</v>
@@ -8831,7 +8831,7 @@
         <v>22</v>
       </c>
       <c r="AT43" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU43" t="n">
         <v>7.4</v>
@@ -8846,13 +8846,13 @@
         <v>26</v>
       </c>
       <c r="AY43" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ43" t="n">
         <v>15.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BB43" t="n">
         <v>10.5</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8908,22 +8908,22 @@
         <v>2.38</v>
       </c>
       <c r="G44" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H44" t="n">
         <v>3.6</v>
       </c>
       <c r="I44" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J44" t="n">
         <v>3.25</v>
       </c>
       <c r="K44" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L44" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
@@ -8950,22 +8950,22 @@
         <v>1.87</v>
       </c>
       <c r="U44" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V44" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W44" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA44" t="n">
         <v>70</v>
@@ -8977,7 +8977,7 @@
         <v>7.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE44" t="n">
         <v>46</v>
@@ -9001,13 +9001,13 @@
         <v>27</v>
       </c>
       <c r="AL44" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM44" t="n">
         <v>580</v>
       </c>
       <c r="AN44" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AO44" t="n">
         <v>60</v>
@@ -9016,7 +9016,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR44" t="n">
         <v>21</v>
@@ -9037,7 +9037,7 @@
         <v>20</v>
       </c>
       <c r="AX44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY44" t="n">
         <v>10</v>
@@ -9064,11 +9064,11 @@
         <v>18</v>
       </c>
       <c r="BG44" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G45" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H45" t="n">
         <v>5.5</v>
@@ -9111,13 +9111,13 @@
         <v>5.8</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K45" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L45" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M45" t="n">
         <v>1.06</v>
@@ -9150,7 +9150,7 @@
         <v>1.2</v>
       </c>
       <c r="W45" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="X45" t="n">
         <v>17.5</v>
@@ -9189,7 +9189,7 @@
         <v>700</v>
       </c>
       <c r="AJ45" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK45" t="n">
         <v>19</v>
@@ -9216,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT45" t="n">
         <v>8</v>
@@ -9252,17 +9252,17 @@
         <v>16</v>
       </c>
       <c r="BE45" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF45" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -9296,13 +9296,13 @@
         <v>1.44</v>
       </c>
       <c r="G46" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H46" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I46" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
         <v>5.5</v>
@@ -9311,73 +9311,73 @@
         <v>5.6</v>
       </c>
       <c r="L46" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M46" t="n">
         <v>1.04</v>
       </c>
       <c r="N46" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P46" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R46" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S46" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T46" t="n">
         <v>1.9</v>
       </c>
       <c r="U46" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W46" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X46" t="n">
         <v>24</v>
       </c>
       <c r="Y46" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Z46" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA46" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB46" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC46" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AE46" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AG46" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI46" t="n">
         <v>100</v>
@@ -9392,10 +9392,10 @@
         <v>40</v>
       </c>
       <c r="AM46" t="n">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN46" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO46" t="n">
         <v>130</v>
@@ -9404,13 +9404,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR46" t="n">
         <v>30</v>
       </c>
       <c r="AS46" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT46" t="n">
         <v>8.800000000000001</v>
@@ -9419,10 +9419,10 @@
         <v>10.5</v>
       </c>
       <c r="AV46" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AW46" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX46" t="n">
         <v>8.4</v>
@@ -9434,10 +9434,10 @@
         <v>21</v>
       </c>
       <c r="BA46" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BB46" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC46" t="n">
         <v>13</v>
@@ -9449,14 +9449,14 @@
         <v>36</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG46" t="n">
         <v>15</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G47" t="n">
         <v>1.79</v>
@@ -9496,16 +9496,16 @@
         <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K47" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L47" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M47" t="n">
         <v>1.06</v>
@@ -9538,19 +9538,19 @@
         <v>1.23</v>
       </c>
       <c r="W47" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X47" t="n">
         <v>15.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="n">
         <v>42</v>
       </c>
       <c r="AA47" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB47" t="n">
         <v>8.4</v>
@@ -9574,7 +9574,7 @@
         <v>22</v>
       </c>
       <c r="AI47" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AJ47" t="n">
         <v>18.5</v>
@@ -9604,7 +9604,7 @@
         <v>16</v>
       </c>
       <c r="AS47" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT47" t="n">
         <v>7.6</v>
@@ -9613,7 +9613,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV47" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AW47" t="n">
         <v>28</v>
@@ -9631,7 +9631,7 @@
         <v>28</v>
       </c>
       <c r="BB47" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC47" t="n">
         <v>14</v>
@@ -9643,14 +9643,14 @@
         <v>29</v>
       </c>
       <c r="BF47" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG47" t="n">
         <v>15.5</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
         <v>4.7</v>
       </c>
       <c r="J48" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K48" t="n">
         <v>3.65</v>
@@ -9714,7 +9714,7 @@
         <v>1.86</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R48" t="n">
         <v>1.32</v>
@@ -9735,7 +9735,7 @@
         <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
         <v>15.5</v>
@@ -9747,7 +9747,7 @@
         <v>110</v>
       </c>
       <c r="AB48" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC48" t="n">
         <v>9.800000000000001</v>
@@ -9783,31 +9783,31 @@
         <v>580</v>
       </c>
       <c r="AN48" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO48" t="n">
         <v>260</v>
       </c>
       <c r="AP48" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR48" t="n">
         <v>28</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AT48" t="n">
         <v>7.8</v>
       </c>
       <c r="AU48" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV48" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AW48" t="n">
         <v>23</v>
@@ -9816,7 +9816,7 @@
         <v>10.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ48" t="n">
         <v>17.5</v>
@@ -9828,7 +9828,7 @@
         <v>20</v>
       </c>
       <c r="BC48" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD48" t="n">
         <v>34</v>
@@ -9840,11 +9840,11 @@
         <v>14</v>
       </c>
       <c r="BG48" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H49" t="n">
         <v>1.25</v>
@@ -9887,10 +9887,10 @@
         <v>1.27</v>
       </c>
       <c r="J49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K49" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L49" t="n">
         <v>1.2</v>
@@ -9899,34 +9899,34 @@
         <v>1.02</v>
       </c>
       <c r="N49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O49" t="n">
         <v>1.14</v>
       </c>
       <c r="P49" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
         <v>1.45</v>
       </c>
       <c r="R49" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="S49" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T49" t="n">
         <v>1.96</v>
       </c>
       <c r="U49" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="V49" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="W49" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X49" t="n">
         <v>44</v>
@@ -9935,25 +9935,25 @@
         <v>14.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA49" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AC49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD49" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE49" t="n">
         <v>13</v>
       </c>
       <c r="AF49" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AG49" t="n">
         <v>50</v>
@@ -9965,10 +9965,10 @@
         <v>32</v>
       </c>
       <c r="AJ49" t="n">
-        <v>470</v>
+        <v>610</v>
       </c>
       <c r="AK49" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AL49" t="n">
         <v>140</v>
@@ -9980,65 +9980,65 @@
         <v>180</v>
       </c>
       <c r="AO49" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AP49" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="AQ49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV49" t="n">
         <v>11</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>10</v>
       </c>
       <c r="AW49" t="n">
         <v>12</v>
       </c>
       <c r="AX49" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AY49" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AZ49" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BA49" t="n">
         <v>26</v>
       </c>
       <c r="BB49" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BC49" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BD49" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BE49" t="n">
         <v>29</v>
       </c>
       <c r="BF49" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BG49" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G50" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H50" t="n">
         <v>5.5</v>
@@ -10084,7 +10084,7 @@
         <v>3.35</v>
       </c>
       <c r="K50" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L50" t="n">
         <v>1.44</v>
@@ -10093,7 +10093,7 @@
         <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O50" t="n">
         <v>1.45</v>
@@ -10102,25 +10102,25 @@
         <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R50" t="n">
         <v>1.23</v>
       </c>
       <c r="S50" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U50" t="n">
         <v>1.74</v>
       </c>
       <c r="V50" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W50" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X50" t="n">
         <v>11</v>
@@ -10141,7 +10141,7 @@
         <v>8.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AE50" t="n">
         <v>700</v>
@@ -10162,7 +10162,7 @@
         <v>21</v>
       </c>
       <c r="AK50" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AL50" t="n">
         <v>120</v>
@@ -10171,7 +10171,7 @@
         <v>580</v>
       </c>
       <c r="AN50" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="AO50" t="n">
         <v>700</v>
@@ -10183,10 +10183,10 @@
         <v>13.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT50" t="n">
         <v>5.8</v>
@@ -10198,7 +10198,7 @@
         <v>20</v>
       </c>
       <c r="AW50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX50" t="n">
         <v>8.4</v>
@@ -10210,7 +10210,7 @@
         <v>21</v>
       </c>
       <c r="BA50" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB50" t="n">
         <v>17</v>
@@ -10219,20 +10219,20 @@
         <v>19.5</v>
       </c>
       <c r="BD50" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF50" t="n">
         <v>14.5</v>
       </c>
       <c r="BG50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -10263,16 +10263,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G51" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H51" t="n">
         <v>4.5</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J51" t="n">
         <v>3.4</v>
@@ -10299,7 +10299,7 @@
         <v>2.08</v>
       </c>
       <c r="R51" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S51" t="n">
         <v>3.8</v>
@@ -10311,10 +10311,10 @@
         <v>1.93</v>
       </c>
       <c r="V51" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W51" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X51" t="n">
         <v>22</v>
@@ -10380,7 +10380,7 @@
         <v>14.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AT51" t="n">
         <v>6</v>
@@ -10389,10 +10389,10 @@
         <v>6.8</v>
       </c>
       <c r="AV51" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX51" t="n">
         <v>8.4</v>
@@ -10401,10 +10401,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ51" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB51" t="n">
         <v>10.5</v>
@@ -10413,20 +10413,20 @@
         <v>10.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE51" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF51" t="n">
         <v>12</v>
       </c>
       <c r="BG51" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -10460,19 +10460,19 @@
         <v>2.12</v>
       </c>
       <c r="G52" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H52" t="n">
         <v>3.4</v>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="K52" t="n">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10481,7 +10481,7 @@
         <v>1.07</v>
       </c>
       <c r="N52" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="O52" t="n">
         <v>1.32</v>
@@ -10490,7 +10490,7 @@
         <v>1.81</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R52" t="n">
         <v>1.18</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -10651,25 +10651,25 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="G53" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="H53" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="I53" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K53" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L53" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M53" t="n">
         <v>1.08</v>
@@ -10681,28 +10681,28 @@
         <v>1.38</v>
       </c>
       <c r="P53" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R53" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S53" t="n">
         <v>3.9</v>
       </c>
       <c r="T53" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U53" t="n">
         <v>1.98</v>
       </c>
       <c r="V53" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W53" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="X53" t="n">
         <v>14</v>
@@ -10717,7 +10717,7 @@
         <v>85</v>
       </c>
       <c r="AB53" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC53" t="n">
         <v>8.800000000000001</v>
@@ -10729,10 +10729,10 @@
         <v>55</v>
       </c>
       <c r="AF53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG53" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH53" t="n">
         <v>22</v>
@@ -10741,10 +10741,10 @@
         <v>70</v>
       </c>
       <c r="AJ53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK53" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL53" t="n">
         <v>50</v>
@@ -10753,13 +10753,13 @@
         <v>140</v>
       </c>
       <c r="AN53" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO53" t="n">
         <v>65</v>
       </c>
       <c r="AP53" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ53" t="n">
         <v>9.199999999999999</v>
@@ -10768,53 +10768,53 @@
         <v>19</v>
       </c>
       <c r="AS53" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT53" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV53" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AW53" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX53" t="n">
         <v>10.5</v>
       </c>
       <c r="AY53" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AZ53" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA53" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB53" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC53" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE53" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BG53" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -10845,10 +10845,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G54" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H54" t="n">
         <v>4.3</v>
@@ -10857,7 +10857,7 @@
         <v>5</v>
       </c>
       <c r="J54" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K54" t="n">
         <v>3.5</v>
@@ -10866,7 +10866,7 @@
         <v>1.48</v>
       </c>
       <c r="M54" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N54" t="n">
         <v>2.66</v>
@@ -10875,7 +10875,7 @@
         <v>1.47</v>
       </c>
       <c r="P54" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q54" t="n">
         <v>2.4</v>
@@ -10896,16 +10896,16 @@
         <v>1.25</v>
       </c>
       <c r="W54" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X54" t="n">
         <v>11.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA54" t="n">
         <v>140</v>
@@ -10914,10 +10914,10 @@
         <v>7.2</v>
       </c>
       <c r="AC54" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD54" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE54" t="n">
         <v>95</v>
@@ -10950,31 +10950,31 @@
         <v>27</v>
       </c>
       <c r="AO54" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP54" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ54" t="n">
         <v>11.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT54" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AU54" t="n">
         <v>6.8</v>
       </c>
       <c r="AV54" t="n">
-        <v>17</v>
+        <v>5.1</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX54" t="n">
         <v>8.199999999999999</v>
@@ -10986,7 +10986,7 @@
         <v>19</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB54" t="n">
         <v>19</v>
@@ -10995,20 +10995,20 @@
         <v>19</v>
       </c>
       <c r="BD54" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF54" t="n">
         <v>18</v>
       </c>
       <c r="BG54" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="G55" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="H55" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J55" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="K55" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L55" t="n">
         <v>1.41</v>
@@ -11069,7 +11069,7 @@
         <v>1.36</v>
       </c>
       <c r="P55" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q55" t="n">
         <v>1.98</v>
@@ -11087,10 +11087,10 @@
         <v>1.11</v>
       </c>
       <c r="V55" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W55" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -11236,13 +11236,13 @@
         <v>5.1</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H56" t="n">
         <v>1.7</v>
       </c>
       <c r="I56" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>3.75</v>
@@ -11257,7 +11257,7 @@
         <v>1.08</v>
       </c>
       <c r="N56" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O56" t="n">
         <v>1.39</v>
@@ -11266,7 +11266,7 @@
         <v>1.84</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R56" t="n">
         <v>1.28</v>
@@ -11290,7 +11290,7 @@
         <v>970</v>
       </c>
       <c r="Y56" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="Z56" t="n">
         <v>970</v>
@@ -11308,7 +11308,7 @@
         <v>970</v>
       </c>
       <c r="AE56" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF56" t="n">
         <v>46</v>
@@ -11341,62 +11341,62 @@
         <v>970</v>
       </c>
       <c r="AP56" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ56" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ56" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR56" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BA56" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="BG56" t="n">
         <v>10.5</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G57" t="n">
         <v>3.25</v>
@@ -11436,76 +11436,76 @@
         <v>2.52</v>
       </c>
       <c r="I57" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J57" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K57" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L57" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="M57" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O57" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P57" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="R57" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S57" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T57" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="U57" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V57" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W57" t="n">
         <v>1.45</v>
       </c>
       <c r="X57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="n">
         <v>50</v>
       </c>
       <c r="AB57" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC57" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD57" t="n">
         <v>15</v>
       </c>
       <c r="AE57" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG57" t="n">
         <v>16.5</v>
@@ -11532,65 +11532,65 @@
         <v>46</v>
       </c>
       <c r="AO57" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP57" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AR57" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AS57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ57" t="n">
         <v>3.95</v>
       </c>
-      <c r="AT57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BA57" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BB57" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC57" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BD57" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BE57" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF57" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG57" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -11651,7 +11651,7 @@
         <v>1.41</v>
       </c>
       <c r="P58" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q58" t="n">
         <v>2.18</v>
@@ -11687,16 +11687,16 @@
         <v>60</v>
       </c>
       <c r="AB58" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD58" t="n">
         <v>15.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF58" t="n">
         <v>21</v>
@@ -11705,7 +11705,7 @@
         <v>15</v>
       </c>
       <c r="AH58" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI58" t="n">
         <v>60</v>
@@ -11726,7 +11726,7 @@
         <v>40</v>
       </c>
       <c r="AO58" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP58" t="n">
         <v>8.199999999999999</v>
@@ -11738,7 +11738,7 @@
         <v>13.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT58" t="n">
         <v>7</v>
@@ -11750,7 +11750,7 @@
         <v>9.6</v>
       </c>
       <c r="AW58" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX58" t="n">
         <v>13</v>
@@ -11762,29 +11762,29 @@
         <v>14</v>
       </c>
       <c r="BA58" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB58" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BC58" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE58" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF58" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG58" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
         <v>4.7</v>
       </c>
       <c r="H59" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I59" t="n">
         <v>2.12</v>
@@ -11830,7 +11830,7 @@
         <v>3.3</v>
       </c>
       <c r="K59" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L59" t="n">
         <v>1.4</v>
@@ -11893,10 +11893,10 @@
         <v>27</v>
       </c>
       <c r="AF59" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG59" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH59" t="n">
         <v>24</v>
@@ -11932,7 +11932,7 @@
         <v>10</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT59" t="n">
         <v>11.5</v>
@@ -11944,41 +11944,41 @@
         <v>9</v>
       </c>
       <c r="AW59" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX59" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY59" t="n">
         <v>15</v>
       </c>
       <c r="AZ59" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA59" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB59" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC59" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC59" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD59" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE59" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF59" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG59" t="n">
         <v>14</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.19</v>
+        <v>160</v>
       </c>
       <c r="G2" t="n">
-        <v>1.22</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2</v>
+        <v>200</v>
       </c>
       <c r="K2" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -793,23 +793,23 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.01</v>
       </c>
-      <c r="W2" t="n">
-        <v>5.1</v>
-      </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
@@ -838,89 +838,89 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.81</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>1.05</v>
       </c>
       <c r="AP2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>250</v>
+        <v>1.33</v>
       </c>
       <c r="AT2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AV2" t="n">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>250</v>
+        <v>1.33</v>
       </c>
       <c r="AX2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>1.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>130</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>26</v>
+        <v>1.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>240</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 19:26:48</t>
+          <t>2026-05-11 21:43:43</t>
         </is>
       </c>
     </row>
@@ -942,186 +942,186 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>10.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>50</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="I3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S3" t="n">
+        <v>40</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>790</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AR3" t="n">
         <v>3.45</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AS3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV3" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AW3" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY3" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="BB3" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="BE3" t="n">
-        <v>70</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="BG3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 19:26:48</t>
+          <t>2026-05-11 21:43:43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,186 +1136,186 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22</v>
+        <v>7.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>1.29</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>1.33</v>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>2.76</v>
+        <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>1.52</v>
+        <v>24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.62</v>
+        <v>200</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="S4" t="n">
-        <v>5.4</v>
+        <v>220</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>1.81</v>
+        <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>990</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.8</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.5</v>
+        <v>380</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="AW4" t="n">
-        <v>27</v>
+        <v>430</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>160</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.5</v>
+        <v>430</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="BC4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF4" t="n">
-        <v>25</v>
+        <v>290</v>
       </c>
       <c r="BG4" t="n">
-        <v>15.5</v>
+        <v>280</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 19:26:48</t>
+          <t>2026-05-11 21:43:43</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="AO5" t="n">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>44</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="BD5" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="BE5" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="BF5" t="n">
-        <v>19.5</v>
+        <v>100</v>
       </c>
       <c r="BG5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 19:26:48</t>
+          <t>2026-05-11 21:43:43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
-        <v>1.89</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>1.94</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>2.74</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>1.29</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>2.06</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>3.05</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF6" t="n">
         <v>14</v>
       </c>
-      <c r="AC6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>34</v>
-      </c>
       <c r="AG6" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="AJ6" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AM6" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
         <v>110</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="AT6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AU6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>30</v>
-      </c>
       <c r="AY6" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BA6" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="BB6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BD6" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="BE6" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.5</v>
+        <v>140</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 19:26:48</t>
+          <t>2026-05-11 21:43:43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="H7" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>2.66</v>
       </c>
       <c r="M7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.07</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>320</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>360</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>140</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>80</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>95</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>210</v>
+      </c>
+      <c r="BE7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>50</v>
-      </c>
       <c r="BF7" t="n">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="BG7" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 19:26:48</t>
+          <t>2026-05-11 21:43:43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,378 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Sport Boys (Per)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="G8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.25</v>
       </c>
-      <c r="H8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="X8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB8" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT8" t="n">
         <v>11</v>
       </c>
-      <c r="Z8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
         <v>10</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
         <v>23</v>
       </c>
       <c r="AX8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.6</v>
+        <v>110</v>
       </c>
       <c r="BF8" t="n">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="BG8" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 19:26:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Peruvian Primera Division</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sport Boys (Per)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Universitario de Deportes</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-05-11 19:26:48</t>
+          <t>2026-05-11 21:43:43</t>
         </is>
       </c>
     </row>
